--- a/Sources/اجمالى بيانات -1000 -شريحة .xlsx
+++ b/Sources/اجمالى بيانات -1000 -شريحة .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Downloads\Rania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD38B934-594F-4244-8FE6-EE83987EC907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6AE984-41C8-4B49-AC16-311D65820DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" tabRatio="710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Original-Amr" sheetId="12" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'N-A'!$A$1:$S$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'N-A'!$A$1:$S$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9842" uniqueCount="2993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9840" uniqueCount="2998">
   <si>
     <t>Status</t>
   </si>
@@ -9015,13 +9015,28 @@
   </si>
   <si>
     <t>vodafon-6</t>
+  </si>
+  <si>
+    <t>SIM_S_Num</t>
+  </si>
+  <si>
+    <t>محول الجبانه</t>
+  </si>
+  <si>
+    <t>محول التدعبم2</t>
+  </si>
+  <si>
+    <t>لوحه توزيع شباس الشهداء</t>
+  </si>
+  <si>
+    <t>لوحةتوزيع محله دياي</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -9080,6 +9095,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -9107,7 +9129,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -9324,13 +9346,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9419,6 +9452,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9467,6 +9509,108 @@
           <bgColor theme="9"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -9977,108 +10121,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
@@ -10093,36 +10135,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11EE1DFE-DEE2-46AC-87D6-FA357B36E279}" name="Table2" displayName="Table2" ref="A1:S87" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47">
-  <autoFilter ref="A1:S87" xr:uid="{92F12B8A-F57D-4CF0-88D5-5B9D481AA0E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{11EE1DFE-DEE2-46AC-87D6-FA357B36E279}" name="Table2" displayName="Table2" ref="A1:S85" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26">
+  <autoFilter ref="A1:S85" xr:uid="{92F12B8A-F57D-4CF0-88D5-5B9D481AA0E6}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{84A1034C-F853-4A31-B10D-232837D28681}" name="Status" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{F5810C29-A013-4E32-98A2-341DCBB34CF5}" name=" Operator" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{A9ADAFD8-E1EC-4968-B96A-E828059643F3}" name=" Dials" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{53C2E04B-6CB2-497A-A8FF-CDE475B1DA6E}" name="Sime" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{F3DEDFBB-5640-4EC2-AE24-9CE29B407E31}" name=" IMSI" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{CE04764B-3C61-4BE4-86FF-01E22B56C5C5}" name=" com" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{D268EA87-CE4B-4D42-B6D1-FE6FC9211FC0}" name=" كود المشترك" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{E0698E51-F42C-4C14-83F0-33E98B9FA7A0}" name=" اسم المشترك" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{61EDFE85-7B0A-410C-8E7A-91541D6C8374}" name=" العنوان" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{FBA213B2-1978-4E55-BC6A-371CC87D9342}" name=" الجهد" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{8126A643-2244-4E4C-8015-185CD3E6855F}" name=" القدرة" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{E204006A-027C-411C-8BEA-91477AE2FA24}" name=" رقم العداد" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{937D8528-F382-4065-B6AC-84ABF1887A19}" name=" كود الشركة" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{69D482FB-236F-4D75-87AD-3DE96D61EECF}" name=" نوع العداد" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{C45CDD66-0D20-4FC6-8880-2D65D5F504D8}" name=" شركة العدادات" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{364D0090-CEFB-4694-857A-4B7301685BC9}" name=" اسم الكشك الموصل بيه العميل" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{8EA3BA1F-95FE-438F-AC76-A5B5BE66F1F8}" name=" اسم المغذي الموصل بيه العميل" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{3C1B0BD1-B9EC-4B1A-93CC-790C2BF5C524}" name=" اسم الهندسة" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{A0CDD035-DD03-4DBB-9C83-5EEBCEF0B8AC}" name=" TYPE" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{84A1034C-F853-4A31-B10D-232837D28681}" name="Status" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{F5810C29-A013-4E32-98A2-341DCBB34CF5}" name=" Operator" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{A9ADAFD8-E1EC-4968-B96A-E828059643F3}" name=" Dials" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{53C2E04B-6CB2-497A-A8FF-CDE475B1DA6E}" name="SIM_S_Num" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{F3DEDFBB-5640-4EC2-AE24-9CE29B407E31}" name=" IMSI" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{CE04764B-3C61-4BE4-86FF-01E22B56C5C5}" name=" com" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{D268EA87-CE4B-4D42-B6D1-FE6FC9211FC0}" name=" كود المشترك" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{E0698E51-F42C-4C14-83F0-33E98B9FA7A0}" name=" اسم المشترك" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{61EDFE85-7B0A-410C-8E7A-91541D6C8374}" name=" العنوان" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{FBA213B2-1978-4E55-BC6A-371CC87D9342}" name=" الجهد" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{8126A643-2244-4E4C-8015-185CD3E6855F}" name=" القدرة" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{E204006A-027C-411C-8BEA-91477AE2FA24}" name=" رقم العداد" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{937D8528-F382-4065-B6AC-84ABF1887A19}" name=" كود الشركة" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{69D482FB-236F-4D75-87AD-3DE96D61EECF}" name=" نوع العداد" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{C45CDD66-0D20-4FC6-8880-2D65D5F504D8}" name=" شركة العدادات" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{364D0090-CEFB-4694-857A-4B7301685BC9}" name=" اسم الكشك الموصل بيه العميل" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{8EA3BA1F-95FE-438F-AC76-A5B5BE66F1F8}" name=" اسم المغذي الموصل بيه العميل" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{3C1B0BD1-B9EC-4B1A-93CC-790C2BF5C524}" name=" اسم الهندسة" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{A0CDD035-DD03-4DBB-9C83-5EEBCEF0B8AC}" name=" TYPE" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S1001" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="A1:S1001" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S1003" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+  <autoFilter ref="A1:S1003" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="‌Direct Match"/>
@@ -10130,25 +10172,25 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Status" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name=" Operator" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name=" Dials" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sime" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name=" IMSI" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name=" com" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name=" كود المشترك" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name=" اسم المشترك" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name=" العنوان" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name=" الجهد" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name=" القدرة" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name=" رقم العداد" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name=" كود الشركة" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name=" نوع العداد" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name=" شركة العدادات" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name=" اسم الكشك الموصل بيه العميل" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name=" اسم المغذي الموصل بيه العميل" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name=" اسم الهندسة" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name=" TYPE" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Status" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name=" Operator" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name=" Dials" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sime" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name=" IMSI" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name=" com" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name=" كود المشترك" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name=" اسم المشترك" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name=" العنوان" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name=" الجهد" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name=" القدرة" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name=" رقم العداد" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name=" كود الشركة" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name=" نوع العداد" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name=" شركة العدادات" dataDxfId="32"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name=" اسم الكشك الموصل بيه العميل" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name=" اسم المغذي الموصل بيه العميل" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name=" اسم الهندسة" dataDxfId="29"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name=" TYPE" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10451,7 +10493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F12B8A-F57D-4CF0-88D5-5B9D481AA0E6}">
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" style="28" bestFit="1" customWidth="1"/>
@@ -10485,8 +10527,8 @@
       <c r="C1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="25" t="s">
-        <v>33</v>
+      <c r="D1" s="30" t="s">
+        <v>2993</v>
       </c>
       <c r="E1" s="25" t="s">
         <v>17</v>
@@ -10691,7 +10733,7 @@
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
@@ -10728,7 +10770,7 @@
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -10765,7 +10807,7 @@
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
@@ -10802,7 +10844,7 @@
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -10839,7 +10881,7 @@
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -10876,7 +10918,7 @@
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -10913,7 +10955,7 @@
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -10950,7 +10992,7 @@
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -10987,7 +11029,7 @@
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -11024,7 +11066,7 @@
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -11061,7 +11103,7 @@
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -11098,7 +11140,7 @@
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -11135,7 +11177,7 @@
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -11172,7 +11214,7 @@
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -11209,7 +11251,7 @@
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -11246,7 +11288,7 @@
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -11283,7 +11325,7 @@
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -11320,7 +11362,7 @@
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -11357,7 +11399,7 @@
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -11394,7 +11436,7 @@
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -11431,7 +11473,7 @@
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -11468,7 +11510,7 @@
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -11505,7 +11547,7 @@
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -11542,7 +11584,7 @@
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
@@ -11579,7 +11621,7 @@
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
@@ -11616,7 +11658,7 @@
       </c>
       <c r="C31"/>
       <c r="D31" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="E31"/>
       <c r="F31"/>
@@ -11653,7 +11695,7 @@
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="E32"/>
       <c r="F32"/>
@@ -11690,7 +11732,7 @@
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -11727,7 +11769,7 @@
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="E34"/>
       <c r="F34"/>
@@ -11764,7 +11806,7 @@
       </c>
       <c r="C35"/>
       <c r="D35" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E35"/>
       <c r="F35"/>
@@ -11801,7 +11843,7 @@
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="E36"/>
       <c r="F36"/>
@@ -11838,7 +11880,7 @@
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="E37"/>
       <c r="F37"/>
@@ -11875,7 +11917,7 @@
       </c>
       <c r="C38"/>
       <c r="D38" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E38"/>
       <c r="F38"/>
@@ -11912,7 +11954,7 @@
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="E39"/>
       <c r="F39"/>
@@ -11949,7 +11991,7 @@
       </c>
       <c r="C40"/>
       <c r="D40" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E40"/>
       <c r="F40"/>
@@ -11986,7 +12028,7 @@
       </c>
       <c r="C41"/>
       <c r="D41" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E41"/>
       <c r="F41"/>
@@ -12023,7 +12065,7 @@
       </c>
       <c r="C42"/>
       <c r="D42" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="E42"/>
       <c r="F42"/>
@@ -12060,7 +12102,7 @@
       </c>
       <c r="C43"/>
       <c r="D43" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="E43"/>
       <c r="F43"/>
@@ -12097,7 +12139,7 @@
       </c>
       <c r="C44"/>
       <c r="D44" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E44"/>
       <c r="F44"/>
@@ -12134,7 +12176,7 @@
       </c>
       <c r="C45"/>
       <c r="D45" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E45"/>
       <c r="F45"/>
@@ -12171,7 +12213,7 @@
       </c>
       <c r="C46"/>
       <c r="D46" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E46"/>
       <c r="F46"/>
@@ -12208,7 +12250,7 @@
       </c>
       <c r="C47"/>
       <c r="D47" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E47"/>
       <c r="F47"/>
@@ -12245,7 +12287,7 @@
       </c>
       <c r="C48"/>
       <c r="D48" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="E48"/>
       <c r="F48"/>
@@ -12282,7 +12324,7 @@
       </c>
       <c r="C49"/>
       <c r="D49" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="E49"/>
       <c r="F49"/>
@@ -12319,7 +12361,7 @@
       </c>
       <c r="C50"/>
       <c r="D50" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E50"/>
       <c r="F50"/>
@@ -12356,7 +12398,7 @@
       </c>
       <c r="C51"/>
       <c r="D51" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="E51"/>
       <c r="F51"/>
@@ -12393,7 +12435,7 @@
       </c>
       <c r="C52"/>
       <c r="D52" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="E52"/>
       <c r="F52"/>
@@ -12430,7 +12472,7 @@
       </c>
       <c r="C53"/>
       <c r="D53" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E53"/>
       <c r="F53"/>
@@ -12467,7 +12509,7 @@
       </c>
       <c r="C54"/>
       <c r="D54" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="E54"/>
       <c r="F54"/>
@@ -12504,7 +12546,7 @@
       </c>
       <c r="C55"/>
       <c r="D55" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E55"/>
       <c r="F55"/>
@@ -12541,7 +12583,7 @@
       </c>
       <c r="C56"/>
       <c r="D56" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="E56"/>
       <c r="F56"/>
@@ -12578,7 +12620,7 @@
       </c>
       <c r="C57"/>
       <c r="D57" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="E57"/>
       <c r="F57"/>
@@ -12615,7 +12657,7 @@
       </c>
       <c r="C58"/>
       <c r="D58" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="E58"/>
       <c r="F58"/>
@@ -12652,7 +12694,7 @@
       </c>
       <c r="C59"/>
       <c r="D59" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
@@ -12689,7 +12731,7 @@
       </c>
       <c r="C60"/>
       <c r="D60" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
@@ -12726,7 +12768,7 @@
       </c>
       <c r="C61"/>
       <c r="D61" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
@@ -12763,7 +12805,7 @@
       </c>
       <c r="C62"/>
       <c r="D62" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
@@ -12800,7 +12842,7 @@
       </c>
       <c r="C63"/>
       <c r="D63" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="E63"/>
       <c r="F63"/>
@@ -12837,7 +12879,7 @@
       </c>
       <c r="C64"/>
       <c r="D64" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E64"/>
       <c r="F64"/>
@@ -12874,7 +12916,7 @@
       </c>
       <c r="C65"/>
       <c r="D65" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
@@ -12911,7 +12953,7 @@
       </c>
       <c r="C66"/>
       <c r="D66" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
@@ -12948,7 +12990,7 @@
       </c>
       <c r="C67"/>
       <c r="D67" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E67"/>
       <c r="F67"/>
@@ -12985,7 +13027,7 @@
       </c>
       <c r="C68"/>
       <c r="D68" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E68"/>
       <c r="F68"/>
@@ -13022,7 +13064,7 @@
       </c>
       <c r="C69"/>
       <c r="D69" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="E69"/>
       <c r="F69"/>
@@ -13059,7 +13101,7 @@
       </c>
       <c r="C70"/>
       <c r="D70" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E70"/>
       <c r="F70"/>
@@ -13096,7 +13138,7 @@
       </c>
       <c r="C71"/>
       <c r="D71" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E71"/>
       <c r="F71"/>
@@ -13133,7 +13175,7 @@
       </c>
       <c r="C72"/>
       <c r="D72" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E72"/>
       <c r="F72"/>
@@ -13170,7 +13212,7 @@
       </c>
       <c r="C73"/>
       <c r="D73" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="E73"/>
       <c r="F73"/>
@@ -13207,7 +13249,7 @@
       </c>
       <c r="C74"/>
       <c r="D74" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="E74"/>
       <c r="F74"/>
@@ -13244,7 +13286,7 @@
       </c>
       <c r="C75"/>
       <c r="D75" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E75"/>
       <c r="F75"/>
@@ -13281,7 +13323,7 @@
       </c>
       <c r="C76"/>
       <c r="D76" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E76"/>
       <c r="F76"/>
@@ -13318,7 +13360,7 @@
       </c>
       <c r="C77"/>
       <c r="D77" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="E77"/>
       <c r="F77"/>
@@ -13355,7 +13397,7 @@
       </c>
       <c r="C78"/>
       <c r="D78" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E78"/>
       <c r="F78"/>
@@ -13392,7 +13434,7 @@
       </c>
       <c r="C79"/>
       <c r="D79" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E79"/>
       <c r="F79"/>
@@ -13429,7 +13471,7 @@
       </c>
       <c r="C80"/>
       <c r="D80" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E80"/>
       <c r="F80"/>
@@ -13466,7 +13508,7 @@
       </c>
       <c r="C81"/>
       <c r="D81" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E81"/>
       <c r="F81"/>
@@ -13503,7 +13545,7 @@
       </c>
       <c r="C82"/>
       <c r="D82" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E82"/>
       <c r="F82"/>
@@ -13540,7 +13582,7 @@
       </c>
       <c r="C83"/>
       <c r="D83" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="E83"/>
       <c r="F83"/>
@@ -13577,7 +13619,7 @@
       </c>
       <c r="C84"/>
       <c r="D84" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E84"/>
       <c r="F84"/>
@@ -13614,7 +13656,7 @@
       </c>
       <c r="C85"/>
       <c r="D85" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="E85"/>
       <c r="F85"/>
@@ -13639,80 +13681,6 @@
         <v>1035</v>
       </c>
       <c r="S85" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19">
-      <c r="A86" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B86" t="s">
-        <v>2992</v>
-      </c>
-      <c r="C86"/>
-      <c r="D86" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M86"/>
-      <c r="N86"/>
-      <c r="O86"/>
-      <c r="P86" t="s">
-        <v>1035</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>1035</v>
-      </c>
-      <c r="R86" t="s">
-        <v>1035</v>
-      </c>
-      <c r="S86" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19">
-      <c r="A87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B87" t="s">
-        <v>2992</v>
-      </c>
-      <c r="C87"/>
-      <c r="D87" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="M87"/>
-      <c r="N87"/>
-      <c r="O87"/>
-      <c r="P87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="R87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="S87" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -13729,7 +13697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1001"/>
+  <dimension ref="A1:S1003"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.140625" style="1" customWidth="1"/>
@@ -17517,7 +17485,7 @@
       <c r="A102" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B102" s="29" t="s">
+      <c r="B102" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -17543,7 +17511,7 @@
       <c r="A103" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B103" s="29" t="s">
+      <c r="B103" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -17569,7 +17537,7 @@
       <c r="A104" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B104" s="29" t="s">
+      <c r="B104" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -17595,7 +17563,7 @@
       <c r="A105" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B105" s="29" t="s">
+      <c r="B105" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -17621,7 +17589,7 @@
       <c r="A106" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B106" s="29" t="s">
+      <c r="B106" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -17647,7 +17615,7 @@
       <c r="A107" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B107" s="29" t="s">
+      <c r="B107" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -17673,7 +17641,7 @@
       <c r="A108" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B108" s="29" t="s">
+      <c r="B108" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -17699,7 +17667,7 @@
       <c r="A109" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B109" s="29" t="s">
+      <c r="B109" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -17725,7 +17693,7 @@
       <c r="A110" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B110" s="29" t="s">
+      <c r="B110" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -17751,7 +17719,7 @@
       <c r="A111" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B111" s="29" t="s">
+      <c r="B111" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -17777,7 +17745,7 @@
       <c r="A112" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B112" s="29" t="s">
+      <c r="B112" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -17803,7 +17771,7 @@
       <c r="A113" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B113" s="29" t="s">
+      <c r="B113" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -17829,7 +17797,7 @@
       <c r="A114" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B114" s="29" t="s">
+      <c r="B114" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -17855,7 +17823,7 @@
       <c r="A115" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B115" s="29" t="s">
+      <c r="B115" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -17881,7 +17849,7 @@
       <c r="A116" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B116" s="29" t="s">
+      <c r="B116" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -17907,7 +17875,7 @@
       <c r="A117" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B117" s="29" t="s">
+      <c r="B117" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -17933,7 +17901,7 @@
       <c r="A118" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B118" s="29" t="s">
+      <c r="B118" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -17959,7 +17927,7 @@
       <c r="A119" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -17985,7 +17953,7 @@
       <c r="A120" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B120" s="29" t="s">
+      <c r="B120" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -18011,7 +17979,7 @@
       <c r="A121" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -18037,7 +18005,7 @@
       <c r="A122" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -18063,7 +18031,7 @@
       <c r="A123" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B123" s="29" t="s">
+      <c r="B123" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -18089,7 +18057,7 @@
       <c r="A124" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B124" s="29" t="s">
+      <c r="B124" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -18115,7 +18083,7 @@
       <c r="A125" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B125" s="29" t="s">
+      <c r="B125" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -18141,7 +18109,7 @@
       <c r="A126" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B126" s="29" t="s">
+      <c r="B126" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -18167,7 +18135,7 @@
       <c r="A127" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B127" s="29" t="s">
+      <c r="B127" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -18193,7 +18161,7 @@
       <c r="A128" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B128" s="29" t="s">
+      <c r="B128" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -18219,7 +18187,7 @@
       <c r="A129" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B129" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -18245,7 +18213,7 @@
       <c r="A130" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B130" s="29" t="s">
+      <c r="B130" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -18271,7 +18239,7 @@
       <c r="A131" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B131" s="29" t="s">
+      <c r="B131" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -18297,7 +18265,7 @@
       <c r="A132" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B132" s="29" t="s">
+      <c r="B132" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -18323,7 +18291,7 @@
       <c r="A133" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B133" s="29" t="s">
+      <c r="B133" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -18349,7 +18317,7 @@
       <c r="A134" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B134" s="29" t="s">
+      <c r="B134" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -18375,7 +18343,7 @@
       <c r="A135" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B135" s="29" t="s">
+      <c r="B135" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -18401,7 +18369,7 @@
       <c r="A136" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B136" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -18427,7 +18395,7 @@
       <c r="A137" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B137" s="29" t="s">
+      <c r="B137" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -18453,7 +18421,7 @@
       <c r="A138" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B138" s="29" t="s">
+      <c r="B138" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -18479,7 +18447,7 @@
       <c r="A139" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B139" s="29" t="s">
+      <c r="B139" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -18505,7 +18473,7 @@
       <c r="A140" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -18531,7 +18499,7 @@
       <c r="A141" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B141" s="29" t="s">
+      <c r="B141" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -18557,7 +18525,7 @@
       <c r="A142" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B142" s="29" t="s">
+      <c r="B142" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -18583,7 +18551,7 @@
       <c r="A143" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -18609,7 +18577,7 @@
       <c r="A144" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B144" s="29" t="s">
+      <c r="B144" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -18635,7 +18603,7 @@
       <c r="A145" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B145" s="29" t="s">
+      <c r="B145" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -18661,7 +18629,7 @@
       <c r="A146" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B146" s="29" t="s">
+      <c r="B146" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -18687,7 +18655,7 @@
       <c r="A147" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B147" s="29" t="s">
+      <c r="B147" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -18713,7 +18681,7 @@
       <c r="A148" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B148" s="29" t="s">
+      <c r="B148" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -18739,7 +18707,7 @@
       <c r="A149" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B149" s="29" t="s">
+      <c r="B149" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -18765,7 +18733,7 @@
       <c r="A150" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B150" s="29" t="s">
+      <c r="B150" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -18791,7 +18759,7 @@
       <c r="A151" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B151" s="29" t="s">
+      <c r="B151" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -18817,7 +18785,7 @@
       <c r="A152" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B152" s="29" t="s">
+      <c r="B152" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -18843,7 +18811,7 @@
       <c r="A153" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B153" s="29" t="s">
+      <c r="B153" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -18869,7 +18837,7 @@
       <c r="A154" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B154" s="29" t="s">
+      <c r="B154" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -18895,7 +18863,7 @@
       <c r="A155" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B155" s="29" t="s">
+      <c r="B155" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D155" s="1" t="s">
@@ -18921,7 +18889,7 @@
       <c r="A156" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B156" s="29" t="s">
+      <c r="B156" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D156" s="1" t="s">
@@ -18947,7 +18915,7 @@
       <c r="A157" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B157" s="29" t="s">
+      <c r="B157" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D157" s="1" t="s">
@@ -18973,7 +18941,7 @@
       <c r="A158" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B158" s="29" t="s">
+      <c r="B158" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -18999,7 +18967,7 @@
       <c r="A159" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B159" s="29" t="s">
+      <c r="B159" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D159" s="1" t="s">
@@ -19025,7 +18993,7 @@
       <c r="A160" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B160" s="29" t="s">
+      <c r="B160" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D160" s="1" t="s">
@@ -19051,7 +19019,7 @@
       <c r="A161" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B161" s="29" t="s">
+      <c r="B161" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -19077,7 +19045,7 @@
       <c r="A162" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B162" s="29" t="s">
+      <c r="B162" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -19103,7 +19071,7 @@
       <c r="A163" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B163" s="29" t="s">
+      <c r="B163" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D163" s="1" t="s">
@@ -19129,7 +19097,7 @@
       <c r="A164" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B164" s="29" t="s">
+      <c r="B164" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -19155,7 +19123,7 @@
       <c r="A165" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B165" s="29" t="s">
+      <c r="B165" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -19181,7 +19149,7 @@
       <c r="A166" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B166" s="29" t="s">
+      <c r="B166" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -19207,7 +19175,7 @@
       <c r="A167" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B167" s="29" t="s">
+      <c r="B167" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -19233,7 +19201,7 @@
       <c r="A168" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B168" s="29" t="s">
+      <c r="B168" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -19259,7 +19227,7 @@
       <c r="A169" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B169" s="29" t="s">
+      <c r="B169" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -19285,7 +19253,7 @@
       <c r="A170" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B170" s="29" t="s">
+      <c r="B170" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D170" s="1" t="s">
@@ -19311,7 +19279,7 @@
       <c r="A171" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B171" s="29" t="s">
+      <c r="B171" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D171" s="1" t="s">
@@ -19337,7 +19305,7 @@
       <c r="A172" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B172" s="29" t="s">
+      <c r="B172" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -19363,7 +19331,7 @@
       <c r="A173" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B173" s="29" t="s">
+      <c r="B173" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -19389,7 +19357,7 @@
       <c r="A174" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B174" s="29" t="s">
+      <c r="B174" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D174" s="1" t="s">
@@ -19415,7 +19383,7 @@
       <c r="A175" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B175" s="29" t="s">
+      <c r="B175" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D175" s="1" t="s">
@@ -19441,7 +19409,7 @@
       <c r="A176" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B176" s="29" t="s">
+      <c r="B176" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -19467,7 +19435,7 @@
       <c r="A177" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B177" s="29" t="s">
+      <c r="B177" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D177" s="1" t="s">
@@ -19493,7 +19461,7 @@
       <c r="A178" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B178" s="29" t="s">
+      <c r="B178" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -19519,7 +19487,7 @@
       <c r="A179" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B179" s="29" t="s">
+      <c r="B179" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D179" s="1" t="s">
@@ -19545,7 +19513,7 @@
       <c r="A180" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B180" s="29" t="s">
+      <c r="B180" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D180" s="1" t="s">
@@ -19571,7 +19539,7 @@
       <c r="A181" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B181" s="29" t="s">
+      <c r="B181" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D181" s="1" t="s">
@@ -19597,7 +19565,7 @@
       <c r="A182" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B182" s="29" t="s">
+      <c r="B182" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D182" s="1" t="s">
@@ -19623,7 +19591,7 @@
       <c r="A183" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B183" s="29" t="s">
+      <c r="B183" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -19649,7 +19617,7 @@
       <c r="A184" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B184" s="29" t="s">
+      <c r="B184" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D184" s="1" t="s">
@@ -19675,7 +19643,7 @@
       <c r="A185" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B185" s="29" t="s">
+      <c r="B185" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D185" s="1" t="s">
@@ -19701,7 +19669,7 @@
       <c r="A186" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B186" s="29" t="s">
+      <c r="B186" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D186" s="1" t="s">
@@ -19727,7 +19695,7 @@
       <c r="A187" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B187" s="29" t="s">
+      <c r="B187" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D187" s="1" t="s">
@@ -19753,7 +19721,7 @@
       <c r="A188" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B188" s="29" t="s">
+      <c r="B188" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D188" s="1" t="s">
@@ -19779,7 +19747,7 @@
       <c r="A189" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B189" s="29" t="s">
+      <c r="B189" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D189" s="1" t="s">
@@ -19805,7 +19773,7 @@
       <c r="A190" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B190" s="29" t="s">
+      <c r="B190" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D190" s="1" t="s">
@@ -19831,7 +19799,7 @@
       <c r="A191" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B191" s="29" t="s">
+      <c r="B191" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D191" s="1" t="s">
@@ -19857,7 +19825,7 @@
       <c r="A192" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B192" s="29" t="s">
+      <c r="B192" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -19883,7 +19851,7 @@
       <c r="A193" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B193" s="29" t="s">
+      <c r="B193" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -19909,7 +19877,7 @@
       <c r="A194" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B194" s="29" t="s">
+      <c r="B194" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -19935,7 +19903,7 @@
       <c r="A195" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B195" s="29" t="s">
+      <c r="B195" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D195" s="1" t="s">
@@ -19961,7 +19929,7 @@
       <c r="A196" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B196" s="29" t="s">
+      <c r="B196" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -19987,7 +19955,7 @@
       <c r="A197" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B197" s="29" t="s">
+      <c r="B197" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -20013,7 +19981,7 @@
       <c r="A198" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B198" s="29" t="s">
+      <c r="B198" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -20039,7 +20007,7 @@
       <c r="A199" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B199" s="29" t="s">
+      <c r="B199" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -20065,7 +20033,7 @@
       <c r="A200" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B200" s="29" t="s">
+      <c r="B200" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -20091,7 +20059,7 @@
       <c r="A201" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B201" s="29" t="s">
+      <c r="B201" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -20117,7 +20085,7 @@
       <c r="A202" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B202" s="29" t="s">
+      <c r="B202" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D202" s="1" t="s">
@@ -20143,7 +20111,7 @@
       <c r="A203" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B203" s="29" t="s">
+      <c r="B203" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -20169,7 +20137,7 @@
       <c r="A204" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B204" s="29" t="s">
+      <c r="B204" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -20195,7 +20163,7 @@
       <c r="A205" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B205" s="29" t="s">
+      <c r="B205" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D205" s="1" t="s">
@@ -20221,7 +20189,7 @@
       <c r="A206" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B206" s="29" t="s">
+      <c r="B206" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D206" s="1" t="s">
@@ -20247,7 +20215,7 @@
       <c r="A207" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B207" s="29" t="s">
+      <c r="B207" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D207" s="1" t="s">
@@ -20273,7 +20241,7 @@
       <c r="A208" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B208" s="29" t="s">
+      <c r="B208" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D208" s="1" t="s">
@@ -20299,7 +20267,7 @@
       <c r="A209" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B209" s="29" t="s">
+      <c r="B209" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D209" s="1" t="s">
@@ -20325,7 +20293,7 @@
       <c r="A210" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B210" s="29" t="s">
+      <c r="B210" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D210" s="1" t="s">
@@ -20351,7 +20319,7 @@
       <c r="A211" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B211" s="29" t="s">
+      <c r="B211" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D211" s="1" t="s">
@@ -20377,7 +20345,7 @@
       <c r="A212" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B212" s="29" t="s">
+      <c r="B212" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D212" s="1" t="s">
@@ -20403,7 +20371,7 @@
       <c r="A213" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B213" s="29" t="s">
+      <c r="B213" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D213" s="1" t="s">
@@ -20429,7 +20397,7 @@
       <c r="A214" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B214" s="29" t="s">
+      <c r="B214" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -20455,7 +20423,7 @@
       <c r="A215" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B215" s="29" t="s">
+      <c r="B215" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D215" s="1" t="s">
@@ -20481,7 +20449,7 @@
       <c r="A216" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B216" s="29" t="s">
+      <c r="B216" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D216" s="1" t="s">
@@ -20507,7 +20475,7 @@
       <c r="A217" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B217" s="29" t="s">
+      <c r="B217" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D217" s="1" t="s">
@@ -20533,7 +20501,7 @@
       <c r="A218" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B218" s="29" t="s">
+      <c r="B218" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D218" s="1" t="s">
@@ -20559,7 +20527,7 @@
       <c r="A219" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B219" s="29" t="s">
+      <c r="B219" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D219" s="1" t="s">
@@ -20585,7 +20553,7 @@
       <c r="A220" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B220" s="29" t="s">
+      <c r="B220" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D220" s="1" t="s">
@@ -20611,7 +20579,7 @@
       <c r="A221" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B221" s="29" t="s">
+      <c r="B221" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D221" s="1" t="s">
@@ -20637,7 +20605,7 @@
       <c r="A222" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B222" s="29" t="s">
+      <c r="B222" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D222" s="1" t="s">
@@ -20663,7 +20631,7 @@
       <c r="A223" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B223" s="29" t="s">
+      <c r="B223" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D223" s="1" t="s">
@@ -20689,7 +20657,7 @@
       <c r="A224" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B224" s="29" t="s">
+      <c r="B224" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D224" s="1" t="s">
@@ -20715,7 +20683,7 @@
       <c r="A225" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B225" s="29" t="s">
+      <c r="B225" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D225" s="1" t="s">
@@ -20741,7 +20709,7 @@
       <c r="A226" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B226" s="29" t="s">
+      <c r="B226" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D226" s="1" t="s">
@@ -20767,7 +20735,7 @@
       <c r="A227" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B227" s="29" t="s">
+      <c r="B227" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D227" s="1" t="s">
@@ -20793,7 +20761,7 @@
       <c r="A228" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B228" s="29" t="s">
+      <c r="B228" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D228" s="1" t="s">
@@ -20819,7 +20787,7 @@
       <c r="A229" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B229" s="29" t="s">
+      <c r="B229" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D229" s="1" t="s">
@@ -20845,7 +20813,7 @@
       <c r="A230" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B230" s="29" t="s">
+      <c r="B230" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D230" s="1" t="s">
@@ -20871,7 +20839,7 @@
       <c r="A231" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B231" s="29" t="s">
+      <c r="B231" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D231" s="1" t="s">
@@ -20897,7 +20865,7 @@
       <c r="A232" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B232" s="29" t="s">
+      <c r="B232" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D232" s="1" t="s">
@@ -20923,7 +20891,7 @@
       <c r="A233" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B233" s="29" t="s">
+      <c r="B233" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D233" s="1" t="s">
@@ -20949,7 +20917,7 @@
       <c r="A234" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B234" s="29" t="s">
+      <c r="B234" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D234" s="1" t="s">
@@ -20975,7 +20943,7 @@
       <c r="A235" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B235" s="29" t="s">
+      <c r="B235" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D235" s="1" t="s">
@@ -21001,7 +20969,7 @@
       <c r="A236" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B236" s="29" t="s">
+      <c r="B236" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D236" s="1" t="s">
@@ -21027,7 +20995,7 @@
       <c r="A237" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B237" s="29" t="s">
+      <c r="B237" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D237" s="1" t="s">
@@ -21053,7 +21021,7 @@
       <c r="A238" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B238" s="29" t="s">
+      <c r="B238" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D238" s="1" t="s">
@@ -21079,7 +21047,7 @@
       <c r="A239" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B239" s="29" t="s">
+      <c r="B239" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D239" s="1" t="s">
@@ -21105,7 +21073,7 @@
       <c r="A240" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B240" s="29" t="s">
+      <c r="B240" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D240" s="1" t="s">
@@ -21131,7 +21099,7 @@
       <c r="A241" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B241" s="29" t="s">
+      <c r="B241" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D241" s="1" t="s">
@@ -21157,7 +21125,7 @@
       <c r="A242" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B242" s="29" t="s">
+      <c r="B242" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D242" s="1" t="s">
@@ -21183,7 +21151,7 @@
       <c r="A243" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B243" s="29" t="s">
+      <c r="B243" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D243" s="1" t="s">
@@ -21209,7 +21177,7 @@
       <c r="A244" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B244" s="29" t="s">
+      <c r="B244" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D244" s="1" t="s">
@@ -21235,7 +21203,7 @@
       <c r="A245" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B245" s="29" t="s">
+      <c r="B245" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D245" s="1" t="s">
@@ -21261,7 +21229,7 @@
       <c r="A246" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B246" s="29" t="s">
+      <c r="B246" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D246" s="1" t="s">
@@ -21287,7 +21255,7 @@
       <c r="A247" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B247" s="29" t="s">
+      <c r="B247" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D247" s="1" t="s">
@@ -21313,7 +21281,7 @@
       <c r="A248" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B248" s="29" t="s">
+      <c r="B248" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D248" s="1" t="s">
@@ -21339,7 +21307,7 @@
       <c r="A249" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B249" s="29" t="s">
+      <c r="B249" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D249" s="1" t="s">
@@ -21365,7 +21333,7 @@
       <c r="A250" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B250" s="29" t="s">
+      <c r="B250" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D250" s="1" t="s">
@@ -21391,7 +21359,7 @@
       <c r="A251" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B251" s="29" t="s">
+      <c r="B251" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D251" s="1" t="s">
@@ -21417,7 +21385,7 @@
       <c r="A252" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B252" s="29" t="s">
+      <c r="B252" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D252" s="1" t="s">
@@ -21443,7 +21411,7 @@
       <c r="A253" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B253" s="29" t="s">
+      <c r="B253" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D253" s="1" t="s">
@@ -21469,7 +21437,7 @@
       <c r="A254" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B254" s="29" t="s">
+      <c r="B254" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D254" s="1" t="s">
@@ -21495,7 +21463,7 @@
       <c r="A255" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B255" s="29" t="s">
+      <c r="B255" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D255" s="1" t="s">
@@ -21521,7 +21489,7 @@
       <c r="A256" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B256" s="29" t="s">
+      <c r="B256" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D256" s="1" t="s">
@@ -21547,7 +21515,7 @@
       <c r="A257" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B257" s="29" t="s">
+      <c r="B257" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D257" s="1" t="s">
@@ -21573,7 +21541,7 @@
       <c r="A258" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B258" s="29" t="s">
+      <c r="B258" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D258" s="1" t="s">
@@ -21599,7 +21567,7 @@
       <c r="A259" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B259" s="29" t="s">
+      <c r="B259" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D259" s="1" t="s">
@@ -21625,7 +21593,7 @@
       <c r="A260" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B260" s="29" t="s">
+      <c r="B260" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D260" s="1" t="s">
@@ -21651,7 +21619,7 @@
       <c r="A261" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B261" s="29" t="s">
+      <c r="B261" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D261" s="1" t="s">
@@ -21677,7 +21645,7 @@
       <c r="A262" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B262" s="29" t="s">
+      <c r="B262" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D262" s="1" t="s">
@@ -21703,7 +21671,7 @@
       <c r="A263" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B263" s="29" t="s">
+      <c r="B263" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D263" s="1" t="s">
@@ -21729,7 +21697,7 @@
       <c r="A264" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B264" s="29" t="s">
+      <c r="B264" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D264" s="1" t="s">
@@ -21755,7 +21723,7 @@
       <c r="A265" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B265" s="29" t="s">
+      <c r="B265" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D265" s="1" t="s">
@@ -21781,7 +21749,7 @@
       <c r="A266" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B266" s="29" t="s">
+      <c r="B266" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D266" s="1" t="s">
@@ -21807,7 +21775,7 @@
       <c r="A267" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B267" s="29" t="s">
+      <c r="B267" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D267" s="1" t="s">
@@ -21833,7 +21801,7 @@
       <c r="A268" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B268" s="29" t="s">
+      <c r="B268" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D268" s="1" t="s">
@@ -21859,7 +21827,7 @@
       <c r="A269" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B269" s="29" t="s">
+      <c r="B269" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D269" s="1" t="s">
@@ -21885,7 +21853,7 @@
       <c r="A270" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B270" s="29" t="s">
+      <c r="B270" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D270" s="1" t="s">
@@ -21911,7 +21879,7 @@
       <c r="A271" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B271" s="29" t="s">
+      <c r="B271" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D271" s="1" t="s">
@@ -21937,7 +21905,7 @@
       <c r="A272" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B272" s="29" t="s">
+      <c r="B272" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D272" s="1" t="s">
@@ -21963,7 +21931,7 @@
       <c r="A273" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B273" s="29" t="s">
+      <c r="B273" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D273" s="1" t="s">
@@ -21989,7 +21957,7 @@
       <c r="A274" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B274" s="29" t="s">
+      <c r="B274" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D274" s="1" t="s">
@@ -22015,7 +21983,7 @@
       <c r="A275" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B275" s="29" t="s">
+      <c r="B275" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D275" s="1" t="s">
@@ -22041,7 +22009,7 @@
       <c r="A276" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B276" s="29" t="s">
+      <c r="B276" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D276" s="1" t="s">
@@ -22067,7 +22035,7 @@
       <c r="A277" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B277" s="29" t="s">
+      <c r="B277" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D277" s="1" t="s">
@@ -22093,7 +22061,7 @@
       <c r="A278" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B278" s="29" t="s">
+      <c r="B278" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D278" s="1" t="s">
@@ -22119,7 +22087,7 @@
       <c r="A279" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B279" s="29" t="s">
+      <c r="B279" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D279" s="1" t="s">
@@ -22145,7 +22113,7 @@
       <c r="A280" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B280" s="29" t="s">
+      <c r="B280" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D280" s="1" t="s">
@@ -22171,7 +22139,7 @@
       <c r="A281" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B281" s="29" t="s">
+      <c r="B281" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D281" s="1" t="s">
@@ -22197,7 +22165,7 @@
       <c r="A282" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B282" s="29" t="s">
+      <c r="B282" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D282" s="1" t="s">
@@ -22223,7 +22191,7 @@
       <c r="A283" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B283" s="29" t="s">
+      <c r="B283" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D283" s="1" t="s">
@@ -22249,7 +22217,7 @@
       <c r="A284" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B284" s="29" t="s">
+      <c r="B284" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D284" s="1" t="s">
@@ -22275,7 +22243,7 @@
       <c r="A285" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B285" s="29" t="s">
+      <c r="B285" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D285" s="1" t="s">
@@ -22301,7 +22269,7 @@
       <c r="A286" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B286" s="29" t="s">
+      <c r="B286" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D286" s="1" t="s">
@@ -22327,7 +22295,7 @@
       <c r="A287" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B287" s="29" t="s">
+      <c r="B287" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D287" s="1" t="s">
@@ -22353,7 +22321,7 @@
       <c r="A288" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B288" s="29" t="s">
+      <c r="B288" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D288" s="1" t="s">
@@ -22379,7 +22347,7 @@
       <c r="A289" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B289" s="29" t="s">
+      <c r="B289" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D289" s="1" t="s">
@@ -22405,7 +22373,7 @@
       <c r="A290" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B290" s="29" t="s">
+      <c r="B290" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D290" s="1" t="s">
@@ -22431,7 +22399,7 @@
       <c r="A291" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B291" s="29" t="s">
+      <c r="B291" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D291" s="1" t="s">
@@ -22457,7 +22425,7 @@
       <c r="A292" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B292" s="29" t="s">
+      <c r="B292" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D292" s="1" t="s">
@@ -22483,7 +22451,7 @@
       <c r="A293" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B293" s="29" t="s">
+      <c r="B293" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D293" s="1" t="s">
@@ -22509,7 +22477,7 @@
       <c r="A294" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B294" s="29" t="s">
+      <c r="B294" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D294" s="1" t="s">
@@ -22535,7 +22503,7 @@
       <c r="A295" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B295" s="29" t="s">
+      <c r="B295" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D295" s="1" t="s">
@@ -22561,7 +22529,7 @@
       <c r="A296" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B296" s="29" t="s">
+      <c r="B296" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D296" s="1" t="s">
@@ -22587,7 +22555,7 @@
       <c r="A297" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B297" s="29" t="s">
+      <c r="B297" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D297" s="1" t="s">
@@ -22613,7 +22581,7 @@
       <c r="A298" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B298" s="29" t="s">
+      <c r="B298" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D298" s="1" t="s">
@@ -22639,7 +22607,7 @@
       <c r="A299" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B299" s="29" t="s">
+      <c r="B299" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D299" s="1" t="s">
@@ -22665,7 +22633,7 @@
       <c r="A300" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B300" s="29" t="s">
+      <c r="B300" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D300" s="1" t="s">
@@ -22691,7 +22659,7 @@
       <c r="A301" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B301" s="29" t="s">
+      <c r="B301" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D301" s="1" t="s">
@@ -22717,7 +22685,7 @@
       <c r="A302" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B302" s="29" t="s">
+      <c r="B302" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D302" s="1" t="s">
@@ -22743,7 +22711,7 @@
       <c r="A303" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B303" s="29" t="s">
+      <c r="B303" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D303" s="1" t="s">
@@ -22769,7 +22737,7 @@
       <c r="A304" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B304" s="29" t="s">
+      <c r="B304" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D304" s="1" t="s">
@@ -22795,7 +22763,7 @@
       <c r="A305" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B305" s="29" t="s">
+      <c r="B305" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D305" s="1" t="s">
@@ -22821,7 +22789,7 @@
       <c r="A306" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B306" s="29" t="s">
+      <c r="B306" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D306" s="1" t="s">
@@ -22847,7 +22815,7 @@
       <c r="A307" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B307" s="29" t="s">
+      <c r="B307" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D307" s="1" t="s">
@@ -22873,7 +22841,7 @@
       <c r="A308" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B308" s="29" t="s">
+      <c r="B308" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D308" s="1" t="s">
@@ -22899,7 +22867,7 @@
       <c r="A309" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B309" s="29" t="s">
+      <c r="B309" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D309" s="1" t="s">
@@ -22925,7 +22893,7 @@
       <c r="A310" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B310" s="29" t="s">
+      <c r="B310" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D310" s="1" t="s">
@@ -22951,7 +22919,7 @@
       <c r="A311" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B311" s="29" t="s">
+      <c r="B311" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D311" s="1" t="s">
@@ -22977,7 +22945,7 @@
       <c r="A312" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B312" s="29" t="s">
+      <c r="B312" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D312" s="1" t="s">
@@ -23003,7 +22971,7 @@
       <c r="A313" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B313" s="29" t="s">
+      <c r="B313" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D313" s="1" t="s">
@@ -23029,7 +22997,7 @@
       <c r="A314" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B314" s="29" t="s">
+      <c r="B314" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D314" s="1" t="s">
@@ -23055,7 +23023,7 @@
       <c r="A315" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B315" s="29" t="s">
+      <c r="B315" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D315" s="1" t="s">
@@ -23081,7 +23049,7 @@
       <c r="A316" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B316" s="29" t="s">
+      <c r="B316" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D316" s="1" t="s">
@@ -23107,7 +23075,7 @@
       <c r="A317" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B317" s="29" t="s">
+      <c r="B317" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D317" s="1" t="s">
@@ -23133,7 +23101,7 @@
       <c r="A318" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B318" s="29" t="s">
+      <c r="B318" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D318" s="1" t="s">
@@ -23159,7 +23127,7 @@
       <c r="A319" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B319" s="29" t="s">
+      <c r="B319" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D319" s="1" t="s">
@@ -23185,7 +23153,7 @@
       <c r="A320" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B320" s="29" t="s">
+      <c r="B320" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D320" s="1" t="s">
@@ -23211,7 +23179,7 @@
       <c r="A321" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B321" s="29" t="s">
+      <c r="B321" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D321" s="1" t="s">
@@ -23237,7 +23205,7 @@
       <c r="A322" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B322" s="29" t="s">
+      <c r="B322" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D322" s="1" t="s">
@@ -23263,7 +23231,7 @@
       <c r="A323" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B323" s="29" t="s">
+      <c r="B323" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D323" s="1" t="s">
@@ -23289,7 +23257,7 @@
       <c r="A324" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B324" s="29" t="s">
+      <c r="B324" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D324" s="1" t="s">
@@ -23315,7 +23283,7 @@
       <c r="A325" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B325" s="29" t="s">
+      <c r="B325" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D325" s="1" t="s">
@@ -23341,7 +23309,7 @@
       <c r="A326" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B326" s="29" t="s">
+      <c r="B326" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D326" s="1" t="s">
@@ -23367,7 +23335,7 @@
       <c r="A327" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B327" s="29" t="s">
+      <c r="B327" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D327" s="1" t="s">
@@ -23393,7 +23361,7 @@
       <c r="A328" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B328" s="29" t="s">
+      <c r="B328" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D328" s="1" t="s">
@@ -23419,7 +23387,7 @@
       <c r="A329" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B329" s="29" t="s">
+      <c r="B329" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D329" s="1" t="s">
@@ -23445,7 +23413,7 @@
       <c r="A330" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B330" s="29" t="s">
+      <c r="B330" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D330" s="1" t="s">
@@ -23471,7 +23439,7 @@
       <c r="A331" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B331" s="29" t="s">
+      <c r="B331" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D331" s="1" t="s">
@@ -23497,7 +23465,7 @@
       <c r="A332" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B332" s="29" t="s">
+      <c r="B332" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D332" s="1" t="s">
@@ -23523,7 +23491,7 @@
       <c r="A333" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B333" s="29" t="s">
+      <c r="B333" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D333" s="1" t="s">
@@ -23549,7 +23517,7 @@
       <c r="A334" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B334" s="29" t="s">
+      <c r="B334" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D334" s="1" t="s">
@@ -23575,7 +23543,7 @@
       <c r="A335" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B335" s="29" t="s">
+      <c r="B335" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D335" s="1" t="s">
@@ -23601,7 +23569,7 @@
       <c r="A336" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B336" s="29" t="s">
+      <c r="B336" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D336" s="1" t="s">
@@ -23627,7 +23595,7 @@
       <c r="A337" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B337" s="29" t="s">
+      <c r="B337" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D337" s="1" t="s">
@@ -23653,7 +23621,7 @@
       <c r="A338" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B338" s="29" t="s">
+      <c r="B338" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D338" s="1" t="s">
@@ -23679,7 +23647,7 @@
       <c r="A339" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B339" s="29" t="s">
+      <c r="B339" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D339" s="1" t="s">
@@ -23705,7 +23673,7 @@
       <c r="A340" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B340" s="29" t="s">
+      <c r="B340" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D340" s="1" t="s">
@@ -23731,7 +23699,7 @@
       <c r="A341" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B341" s="29" t="s">
+      <c r="B341" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D341" s="1" t="s">
@@ -23757,7 +23725,7 @@
       <c r="A342" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B342" s="29" t="s">
+      <c r="B342" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D342" s="1" t="s">
@@ -23783,7 +23751,7 @@
       <c r="A343" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B343" s="29" t="s">
+      <c r="B343" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D343" s="1" t="s">
@@ -23809,7 +23777,7 @@
       <c r="A344" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B344" s="29" t="s">
+      <c r="B344" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D344" s="1" t="s">
@@ -23835,7 +23803,7 @@
       <c r="A345" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B345" s="29" t="s">
+      <c r="B345" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D345" s="1" t="s">
@@ -23861,7 +23829,7 @@
       <c r="A346" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B346" s="29" t="s">
+      <c r="B346" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D346" s="1" t="s">
@@ -23887,7 +23855,7 @@
       <c r="A347" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B347" s="29" t="s">
+      <c r="B347" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D347" s="1" t="s">
@@ -23913,7 +23881,7 @@
       <c r="A348" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B348" s="29" t="s">
+      <c r="B348" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D348" s="1" t="s">
@@ -23939,7 +23907,7 @@
       <c r="A349" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B349" s="29" t="s">
+      <c r="B349" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D349" s="1" t="s">
@@ -23965,7 +23933,7 @@
       <c r="A350" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B350" s="29" t="s">
+      <c r="B350" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D350" s="1" t="s">
@@ -23991,7 +23959,7 @@
       <c r="A351" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B351" s="29" t="s">
+      <c r="B351" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D351" s="1" t="s">
@@ -24017,7 +23985,7 @@
       <c r="A352" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B352" s="29" t="s">
+      <c r="B352" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D352" s="1" t="s">
@@ -24043,7 +24011,7 @@
       <c r="A353" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B353" s="29" t="s">
+      <c r="B353" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D353" s="1" t="s">
@@ -24069,7 +24037,7 @@
       <c r="A354" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B354" s="29" t="s">
+      <c r="B354" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D354" s="1" t="s">
@@ -24095,7 +24063,7 @@
       <c r="A355" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B355" s="29" t="s">
+      <c r="B355" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D355" s="1" t="s">
@@ -24121,7 +24089,7 @@
       <c r="A356" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B356" s="29" t="s">
+      <c r="B356" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D356" s="1" t="s">
@@ -24147,7 +24115,7 @@
       <c r="A357" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B357" s="29" t="s">
+      <c r="B357" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D357" s="1" t="s">
@@ -24173,7 +24141,7 @@
       <c r="A358" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B358" s="29" t="s">
+      <c r="B358" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D358" s="1" t="s">
@@ -24199,7 +24167,7 @@
       <c r="A359" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B359" s="29" t="s">
+      <c r="B359" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D359" s="1" t="s">
@@ -24225,7 +24193,7 @@
       <c r="A360" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B360" s="29" t="s">
+      <c r="B360" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D360" s="1" t="s">
@@ -24251,7 +24219,7 @@
       <c r="A361" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B361" s="29" t="s">
+      <c r="B361" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D361" s="1" t="s">
@@ -24277,7 +24245,7 @@
       <c r="A362" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B362" s="29" t="s">
+      <c r="B362" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D362" s="1" t="s">
@@ -24303,7 +24271,7 @@
       <c r="A363" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B363" s="29" t="s">
+      <c r="B363" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D363" s="1" t="s">
@@ -24329,7 +24297,7 @@
       <c r="A364" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B364" s="29" t="s">
+      <c r="B364" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D364" s="1" t="s">
@@ -24355,7 +24323,7 @@
       <c r="A365" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B365" s="29" t="s">
+      <c r="B365" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D365" s="1" t="s">
@@ -24381,7 +24349,7 @@
       <c r="A366" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B366" s="29" t="s">
+      <c r="B366" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D366" s="1" t="s">
@@ -24407,7 +24375,7 @@
       <c r="A367" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B367" s="29" t="s">
+      <c r="B367" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D367" s="1" t="s">
@@ -24433,7 +24401,7 @@
       <c r="A368" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B368" s="29" t="s">
+      <c r="B368" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D368" s="1" t="s">
@@ -24459,7 +24427,7 @@
       <c r="A369" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B369" s="29" t="s">
+      <c r="B369" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D369" s="1" t="s">
@@ -24485,7 +24453,7 @@
       <c r="A370" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B370" s="29" t="s">
+      <c r="B370" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D370" s="1" t="s">
@@ -24511,7 +24479,7 @@
       <c r="A371" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B371" s="29" t="s">
+      <c r="B371" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D371" s="1" t="s">
@@ -24537,7 +24505,7 @@
       <c r="A372" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B372" s="29" t="s">
+      <c r="B372" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D372" s="1" t="s">
@@ -24563,7 +24531,7 @@
       <c r="A373" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B373" s="29" t="s">
+      <c r="B373" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D373" s="1" t="s">
@@ -24589,7 +24557,7 @@
       <c r="A374" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B374" s="29" t="s">
+      <c r="B374" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D374" s="1" t="s">
@@ -24615,7 +24583,7 @@
       <c r="A375" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B375" s="29" t="s">
+      <c r="B375" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D375" s="1" t="s">
@@ -24641,7 +24609,7 @@
       <c r="A376" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B376" s="29" t="s">
+      <c r="B376" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D376" s="1" t="s">
@@ -24667,7 +24635,7 @@
       <c r="A377" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B377" s="29" t="s">
+      <c r="B377" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D377" s="1" t="s">
@@ -24693,7 +24661,7 @@
       <c r="A378" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B378" s="29" t="s">
+      <c r="B378" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D378" s="1" t="s">
@@ -24719,7 +24687,7 @@
       <c r="A379" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B379" s="29" t="s">
+      <c r="B379" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D379" s="1" t="s">
@@ -24745,7 +24713,7 @@
       <c r="A380" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B380" s="29" t="s">
+      <c r="B380" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D380" s="1" t="s">
@@ -24771,7 +24739,7 @@
       <c r="A381" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B381" s="29" t="s">
+      <c r="B381" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D381" s="1" t="s">
@@ -24797,7 +24765,7 @@
       <c r="A382" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B382" s="29" t="s">
+      <c r="B382" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D382" s="1" t="s">
@@ -24823,7 +24791,7 @@
       <c r="A383" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B383" s="29" t="s">
+      <c r="B383" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D383" s="1" t="s">
@@ -24849,7 +24817,7 @@
       <c r="A384" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B384" s="29" t="s">
+      <c r="B384" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D384" s="1" t="s">
@@ -24875,7 +24843,7 @@
       <c r="A385" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B385" s="29" t="s">
+      <c r="B385" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D385" s="1" t="s">
@@ -24901,7 +24869,7 @@
       <c r="A386" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B386" s="29" t="s">
+      <c r="B386" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D386" s="1" t="s">
@@ -24927,7 +24895,7 @@
       <c r="A387" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B387" s="29" t="s">
+      <c r="B387" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D387" s="1" t="s">
@@ -24953,7 +24921,7 @@
       <c r="A388" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B388" s="29" t="s">
+      <c r="B388" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D388" s="1" t="s">
@@ -24979,7 +24947,7 @@
       <c r="A389" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B389" s="29" t="s">
+      <c r="B389" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D389" s="1" t="s">
@@ -25005,7 +24973,7 @@
       <c r="A390" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B390" s="29" t="s">
+      <c r="B390" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D390" s="1" t="s">
@@ -25031,7 +24999,7 @@
       <c r="A391" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B391" s="29" t="s">
+      <c r="B391" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D391" s="1" t="s">
@@ -25057,7 +25025,7 @@
       <c r="A392" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B392" s="29" t="s">
+      <c r="B392" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D392" s="1" t="s">
@@ -25083,7 +25051,7 @@
       <c r="A393" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B393" s="29" t="s">
+      <c r="B393" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D393" s="1" t="s">
@@ -25109,7 +25077,7 @@
       <c r="A394" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B394" s="29" t="s">
+      <c r="B394" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D394" s="1" t="s">
@@ -25135,7 +25103,7 @@
       <c r="A395" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B395" s="29" t="s">
+      <c r="B395" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D395" s="1" t="s">
@@ -25161,7 +25129,7 @@
       <c r="A396" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B396" s="29" t="s">
+      <c r="B396" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D396" s="1" t="s">
@@ -25187,7 +25155,7 @@
       <c r="A397" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B397" s="29" t="s">
+      <c r="B397" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D397" s="1" t="s">
@@ -25213,7 +25181,7 @@
       <c r="A398" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B398" s="29" t="s">
+      <c r="B398" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D398" s="1" t="s">
@@ -25239,7 +25207,7 @@
       <c r="A399" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B399" s="29" t="s">
+      <c r="B399" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D399" s="1" t="s">
@@ -25265,7 +25233,7 @@
       <c r="A400" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B400" s="29" t="s">
+      <c r="B400" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D400" s="1" t="s">
@@ -25291,7 +25259,7 @@
       <c r="A401" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B401" s="29" t="s">
+      <c r="B401" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D401" s="1" t="s">
@@ -25317,7 +25285,7 @@
       <c r="A402" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B402" s="29" t="s">
+      <c r="B402" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D402" s="1" t="s">
@@ -25343,7 +25311,7 @@
       <c r="A403" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B403" s="29" t="s">
+      <c r="B403" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D403" s="1" t="s">
@@ -25369,7 +25337,7 @@
       <c r="A404" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B404" s="29" t="s">
+      <c r="B404" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D404" s="1" t="s">
@@ -25395,7 +25363,7 @@
       <c r="A405" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B405" s="29" t="s">
+      <c r="B405" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D405" s="1" t="s">
@@ -25421,7 +25389,7 @@
       <c r="A406" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B406" s="29" t="s">
+      <c r="B406" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D406" s="1" t="s">
@@ -25447,7 +25415,7 @@
       <c r="A407" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B407" s="29" t="s">
+      <c r="B407" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D407" s="1" t="s">
@@ -25473,7 +25441,7 @@
       <c r="A408" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B408" s="29" t="s">
+      <c r="B408" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D408" s="1" t="s">
@@ -25499,7 +25467,7 @@
       <c r="A409" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B409" s="29" t="s">
+      <c r="B409" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D409" s="1" t="s">
@@ -25525,7 +25493,7 @@
       <c r="A410" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B410" s="29" t="s">
+      <c r="B410" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D410" s="1" t="s">
@@ -25551,7 +25519,7 @@
       <c r="A411" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B411" s="29" t="s">
+      <c r="B411" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D411" s="1" t="s">
@@ -25577,7 +25545,7 @@
       <c r="A412" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B412" s="29" t="s">
+      <c r="B412" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D412" s="1" t="s">
@@ -25603,7 +25571,7 @@
       <c r="A413" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B413" s="29" t="s">
+      <c r="B413" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D413" s="1" t="s">
@@ -25629,7 +25597,7 @@
       <c r="A414" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B414" s="29" t="s">
+      <c r="B414" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D414" s="1" t="s">
@@ -25655,7 +25623,7 @@
       <c r="A415" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B415" s="29" t="s">
+      <c r="B415" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D415" s="1" t="s">
@@ -25681,7 +25649,7 @@
       <c r="A416" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B416" s="29" t="s">
+      <c r="B416" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D416" s="1" t="s">
@@ -25707,7 +25675,7 @@
       <c r="A417" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B417" s="29" t="s">
+      <c r="B417" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D417" s="1" t="s">
@@ -25733,7 +25701,7 @@
       <c r="A418" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B418" s="29" t="s">
+      <c r="B418" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D418" s="1" t="s">
@@ -25759,7 +25727,7 @@
       <c r="A419" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B419" s="29" t="s">
+      <c r="B419" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D419" s="1" t="s">
@@ -25785,7 +25753,7 @@
       <c r="A420" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B420" s="29" t="s">
+      <c r="B420" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D420" s="1" t="s">
@@ -25811,7 +25779,7 @@
       <c r="A421" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B421" s="29" t="s">
+      <c r="B421" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D421" s="1" t="s">
@@ -25837,7 +25805,7 @@
       <c r="A422" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B422" s="29" t="s">
+      <c r="B422" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D422" s="1" t="s">
@@ -25863,7 +25831,7 @@
       <c r="A423" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B423" s="29" t="s">
+      <c r="B423" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D423" s="1" t="s">
@@ -25889,7 +25857,7 @@
       <c r="A424" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B424" s="29" t="s">
+      <c r="B424" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D424" s="1" t="s">
@@ -25915,7 +25883,7 @@
       <c r="A425" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B425" s="29" t="s">
+      <c r="B425" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D425" s="1" t="s">
@@ -25941,7 +25909,7 @@
       <c r="A426" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B426" s="29" t="s">
+      <c r="B426" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D426" s="1" t="s">
@@ -25967,7 +25935,7 @@
       <c r="A427" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B427" s="29" t="s">
+      <c r="B427" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D427" s="1" t="s">
@@ -25993,7 +25961,7 @@
       <c r="A428" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B428" s="29" t="s">
+      <c r="B428" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D428" s="1" t="s">
@@ -26019,7 +25987,7 @@
       <c r="A429" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B429" s="29" t="s">
+      <c r="B429" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D429" s="1" t="s">
@@ -26045,7 +26013,7 @@
       <c r="A430" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B430" s="29" t="s">
+      <c r="B430" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D430" s="1" t="s">
@@ -26071,7 +26039,7 @@
       <c r="A431" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B431" s="29" t="s">
+      <c r="B431" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D431" s="1" t="s">
@@ -26097,7 +26065,7 @@
       <c r="A432" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B432" s="29" t="s">
+      <c r="B432" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D432" s="1" t="s">
@@ -26123,7 +26091,7 @@
       <c r="A433" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B433" s="29" t="s">
+      <c r="B433" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D433" s="1" t="s">
@@ -26149,7 +26117,7 @@
       <c r="A434" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B434" s="29" t="s">
+      <c r="B434" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D434" s="1" t="s">
@@ -26175,7 +26143,7 @@
       <c r="A435" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B435" s="29" t="s">
+      <c r="B435" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D435" s="1" t="s">
@@ -26201,7 +26169,7 @@
       <c r="A436" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B436" s="29" t="s">
+      <c r="B436" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D436" s="1" t="s">
@@ -26227,7 +26195,7 @@
       <c r="A437" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B437" s="29" t="s">
+      <c r="B437" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D437" s="1" t="s">
@@ -26253,7 +26221,7 @@
       <c r="A438" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B438" s="29" t="s">
+      <c r="B438" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D438" s="1" t="s">
@@ -26279,7 +26247,7 @@
       <c r="A439" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B439" s="29" t="s">
+      <c r="B439" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D439" s="1" t="s">
@@ -26305,7 +26273,7 @@
       <c r="A440" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B440" s="29" t="s">
+      <c r="B440" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D440" s="1" t="s">
@@ -26331,7 +26299,7 @@
       <c r="A441" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B441" s="29" t="s">
+      <c r="B441" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D441" s="1" t="s">
@@ -26357,7 +26325,7 @@
       <c r="A442" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B442" s="29" t="s">
+      <c r="B442" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D442" s="1" t="s">
@@ -26383,7 +26351,7 @@
       <c r="A443" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B443" s="29" t="s">
+      <c r="B443" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D443" s="1" t="s">
@@ -26409,7 +26377,7 @@
       <c r="A444" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B444" s="29" t="s">
+      <c r="B444" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D444" s="1" t="s">
@@ -26435,7 +26403,7 @@
       <c r="A445" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B445" s="29" t="s">
+      <c r="B445" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D445" s="1" t="s">
@@ -26461,7 +26429,7 @@
       <c r="A446" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B446" s="29" t="s">
+      <c r="B446" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D446" s="1" t="s">
@@ -26487,7 +26455,7 @@
       <c r="A447" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B447" s="29" t="s">
+      <c r="B447" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D447" s="1" t="s">
@@ -26513,7 +26481,7 @@
       <c r="A448" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B448" s="29" t="s">
+      <c r="B448" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D448" s="1" t="s">
@@ -26539,7 +26507,7 @@
       <c r="A449" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B449" s="29" t="s">
+      <c r="B449" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D449" s="1" t="s">
@@ -26565,7 +26533,7 @@
       <c r="A450" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B450" s="29" t="s">
+      <c r="B450" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D450" s="1" t="s">
@@ -26591,7 +26559,7 @@
       <c r="A451" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B451" s="29" t="s">
+      <c r="B451" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D451" s="1" t="s">
@@ -26617,7 +26585,7 @@
       <c r="A452" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B452" s="29" t="s">
+      <c r="B452" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D452" s="1" t="s">
@@ -26643,7 +26611,7 @@
       <c r="A453" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B453" s="29" t="s">
+      <c r="B453" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D453" s="1" t="s">
@@ -26669,7 +26637,7 @@
       <c r="A454" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B454" s="29" t="s">
+      <c r="B454" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D454" s="1" t="s">
@@ -26695,7 +26663,7 @@
       <c r="A455" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B455" s="29" t="s">
+      <c r="B455" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D455" s="1" t="s">
@@ -26721,7 +26689,7 @@
       <c r="A456" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B456" s="29" t="s">
+      <c r="B456" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D456" s="1" t="s">
@@ -26747,7 +26715,7 @@
       <c r="A457" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B457" s="29" t="s">
+      <c r="B457" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D457" s="1" t="s">
@@ -26773,7 +26741,7 @@
       <c r="A458" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B458" s="29" t="s">
+      <c r="B458" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D458" s="1" t="s">
@@ -26799,7 +26767,7 @@
       <c r="A459" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B459" s="29" t="s">
+      <c r="B459" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D459" s="1" t="s">
@@ -26825,7 +26793,7 @@
       <c r="A460" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B460" s="29" t="s">
+      <c r="B460" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D460" s="1" t="s">
@@ -26851,7 +26819,7 @@
       <c r="A461" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B461" s="29" t="s">
+      <c r="B461" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D461" s="1" t="s">
@@ -26877,7 +26845,7 @@
       <c r="A462" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B462" s="29" t="s">
+      <c r="B462" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D462" s="1" t="s">
@@ -26903,7 +26871,7 @@
       <c r="A463" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B463" s="29" t="s">
+      <c r="B463" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D463" s="1" t="s">
@@ -26929,7 +26897,7 @@
       <c r="A464" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B464" s="29" t="s">
+      <c r="B464" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D464" s="1" t="s">
@@ -26955,7 +26923,7 @@
       <c r="A465" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B465" s="29" t="s">
+      <c r="B465" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D465" s="1" t="s">
@@ -26981,7 +26949,7 @@
       <c r="A466" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B466" s="29" t="s">
+      <c r="B466" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D466" s="1" t="s">
@@ -27007,7 +26975,7 @@
       <c r="A467" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B467" s="29" t="s">
+      <c r="B467" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D467" s="1" t="s">
@@ -27033,7 +27001,7 @@
       <c r="A468" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B468" s="29" t="s">
+      <c r="B468" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D468" s="1" t="s">
@@ -27059,7 +27027,7 @@
       <c r="A469" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B469" s="29" t="s">
+      <c r="B469" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D469" s="1" t="s">
@@ -27085,7 +27053,7 @@
       <c r="A470" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B470" s="29" t="s">
+      <c r="B470" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D470" s="1" t="s">
@@ -27111,7 +27079,7 @@
       <c r="A471" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B471" s="29" t="s">
+      <c r="B471" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D471" s="1" t="s">
@@ -27137,7 +27105,7 @@
       <c r="A472" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B472" s="29" t="s">
+      <c r="B472" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D472" s="1" t="s">
@@ -27163,7 +27131,7 @@
       <c r="A473" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B473" s="29" t="s">
+      <c r="B473" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D473" s="1" t="s">
@@ -27189,7 +27157,7 @@
       <c r="A474" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B474" s="29" t="s">
+      <c r="B474" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D474" s="1" t="s">
@@ -27215,7 +27183,7 @@
       <c r="A475" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B475" s="29" t="s">
+      <c r="B475" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D475" s="1" t="s">
@@ -27241,7 +27209,7 @@
       <c r="A476" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B476" s="29" t="s">
+      <c r="B476" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D476" s="1" t="s">
@@ -27267,7 +27235,7 @@
       <c r="A477" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B477" s="29" t="s">
+      <c r="B477" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D477" s="1" t="s">
@@ -27293,7 +27261,7 @@
       <c r="A478" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B478" s="29" t="s">
+      <c r="B478" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D478" s="1" t="s">
@@ -27319,7 +27287,7 @@
       <c r="A479" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B479" s="29" t="s">
+      <c r="B479" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D479" s="1" t="s">
@@ -27345,7 +27313,7 @@
       <c r="A480" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B480" s="29" t="s">
+      <c r="B480" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D480" s="1" t="s">
@@ -27371,7 +27339,7 @@
       <c r="A481" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B481" s="29" t="s">
+      <c r="B481" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D481" s="1" t="s">
@@ -27397,7 +27365,7 @@
       <c r="A482" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B482" s="29" t="s">
+      <c r="B482" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D482" s="1" t="s">
@@ -27423,7 +27391,7 @@
       <c r="A483" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B483" s="29" t="s">
+      <c r="B483" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D483" s="1" t="s">
@@ -27449,7 +27417,7 @@
       <c r="A484" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B484" s="29" t="s">
+      <c r="B484" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D484" s="1" t="s">
@@ -27475,7 +27443,7 @@
       <c r="A485" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B485" s="29" t="s">
+      <c r="B485" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D485" s="1" t="s">
@@ -27501,7 +27469,7 @@
       <c r="A486" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B486" s="29" t="s">
+      <c r="B486" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D486" s="1" t="s">
@@ -27527,7 +27495,7 @@
       <c r="A487" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B487" s="29" t="s">
+      <c r="B487" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D487" s="1" t="s">
@@ -27553,7 +27521,7 @@
       <c r="A488" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B488" s="29" t="s">
+      <c r="B488" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D488" s="1" t="s">
@@ -27579,7 +27547,7 @@
       <c r="A489" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B489" s="29" t="s">
+      <c r="B489" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D489" s="1" t="s">
@@ -27605,7 +27573,7 @@
       <c r="A490" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B490" s="29" t="s">
+      <c r="B490" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D490" s="1" t="s">
@@ -27631,7 +27599,7 @@
       <c r="A491" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B491" s="29" t="s">
+      <c r="B491" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D491" s="1" t="s">
@@ -27657,7 +27625,7 @@
       <c r="A492" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B492" s="29" t="s">
+      <c r="B492" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D492" s="1" t="s">
@@ -27683,7 +27651,7 @@
       <c r="A493" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B493" s="29" t="s">
+      <c r="B493" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D493" s="1" t="s">
@@ -27709,7 +27677,7 @@
       <c r="A494" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B494" s="29" t="s">
+      <c r="B494" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D494" s="1" t="s">
@@ -27735,7 +27703,7 @@
       <c r="A495" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B495" s="29" t="s">
+      <c r="B495" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D495" s="1" t="s">
@@ -27761,7 +27729,7 @@
       <c r="A496" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B496" s="29" t="s">
+      <c r="B496" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D496" s="1" t="s">
@@ -27787,7 +27755,7 @@
       <c r="A497" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B497" s="29" t="s">
+      <c r="B497" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D497" s="1" t="s">
@@ -27813,7 +27781,7 @@
       <c r="A498" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B498" s="29" t="s">
+      <c r="B498" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D498" s="1" t="s">
@@ -27839,7 +27807,7 @@
       <c r="A499" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B499" s="29" t="s">
+      <c r="B499" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D499" s="1" t="s">
@@ -27865,7 +27833,7 @@
       <c r="A500" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B500" s="29" t="s">
+      <c r="B500" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D500" s="1" t="s">
@@ -27891,7 +27859,7 @@
       <c r="A501" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B501" s="29" t="s">
+      <c r="B501" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D501" s="1" t="s">
@@ -27917,7 +27885,7 @@
       <c r="A502" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B502" s="29" t="s">
+      <c r="B502" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D502" s="1" t="s">
@@ -27943,7 +27911,7 @@
       <c r="A503" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B503" s="29" t="s">
+      <c r="B503" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D503" s="1" t="s">
@@ -27969,7 +27937,7 @@
       <c r="A504" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B504" s="29" t="s">
+      <c r="B504" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D504" s="1" t="s">
@@ -27995,7 +27963,7 @@
       <c r="A505" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B505" s="29" t="s">
+      <c r="B505" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D505" s="1" t="s">
@@ -28021,7 +27989,7 @@
       <c r="A506" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B506" s="29" t="s">
+      <c r="B506" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D506" s="1" t="s">
@@ -28047,7 +28015,7 @@
       <c r="A507" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B507" s="29" t="s">
+      <c r="B507" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D507" s="1" t="s">
@@ -28073,7 +28041,7 @@
       <c r="A508" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B508" s="29" t="s">
+      <c r="B508" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D508" s="1" t="s">
@@ -28099,7 +28067,7 @@
       <c r="A509" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B509" s="29" t="s">
+      <c r="B509" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D509" s="1" t="s">
@@ -28125,7 +28093,7 @@
       <c r="A510" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B510" s="29" t="s">
+      <c r="B510" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D510" s="1" t="s">
@@ -28151,7 +28119,7 @@
       <c r="A511" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B511" s="29" t="s">
+      <c r="B511" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D511" s="1" t="s">
@@ -28177,7 +28145,7 @@
       <c r="A512" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B512" s="29" t="s">
+      <c r="B512" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D512" s="1" t="s">
@@ -28203,7 +28171,7 @@
       <c r="A513" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B513" s="29" t="s">
+      <c r="B513" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D513" s="1" t="s">
@@ -28229,7 +28197,7 @@
       <c r="A514" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B514" s="29" t="s">
+      <c r="B514" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D514" s="1" t="s">
@@ -28255,7 +28223,7 @@
       <c r="A515" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B515" s="29" t="s">
+      <c r="B515" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D515" s="1" t="s">
@@ -28281,7 +28249,7 @@
       <c r="A516" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B516" s="29" t="s">
+      <c r="B516" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D516" s="1" t="s">
@@ -28307,7 +28275,7 @@
       <c r="A517" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B517" s="29" t="s">
+      <c r="B517" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D517" s="1" t="s">
@@ -28333,7 +28301,7 @@
       <c r="A518" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B518" s="29" t="s">
+      <c r="B518" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D518" s="1" t="s">
@@ -28359,7 +28327,7 @@
       <c r="A519" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B519" s="29" t="s">
+      <c r="B519" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D519" s="1" t="s">
@@ -28385,7 +28353,7 @@
       <c r="A520" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B520" s="29" t="s">
+      <c r="B520" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D520" s="1" t="s">
@@ -28411,7 +28379,7 @@
       <c r="A521" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B521" s="29" t="s">
+      <c r="B521" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D521" s="1" t="s">
@@ -28437,7 +28405,7 @@
       <c r="A522" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B522" s="29" t="s">
+      <c r="B522" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D522" s="1" t="s">
@@ -28463,7 +28431,7 @@
       <c r="A523" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B523" s="29" t="s">
+      <c r="B523" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D523" s="1" t="s">
@@ -28489,7 +28457,7 @@
       <c r="A524" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B524" s="29" t="s">
+      <c r="B524" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D524" s="1" t="s">
@@ -28515,7 +28483,7 @@
       <c r="A525" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B525" s="29" t="s">
+      <c r="B525" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D525" s="1" t="s">
@@ -28541,7 +28509,7 @@
       <c r="A526" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B526" s="29" t="s">
+      <c r="B526" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D526" s="1" t="s">
@@ -28567,7 +28535,7 @@
       <c r="A527" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B527" s="29" t="s">
+      <c r="B527" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D527" s="1" t="s">
@@ -28593,7 +28561,7 @@
       <c r="A528" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B528" s="29" t="s">
+      <c r="B528" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D528" s="1" t="s">
@@ -28619,7 +28587,7 @@
       <c r="A529" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B529" s="29" t="s">
+      <c r="B529" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D529" s="1" t="s">
@@ -28645,7 +28613,7 @@
       <c r="A530" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B530" s="29" t="s">
+      <c r="B530" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D530" s="1" t="s">
@@ -28671,7 +28639,7 @@
       <c r="A531" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B531" s="29" t="s">
+      <c r="B531" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D531" s="1" t="s">
@@ -28697,7 +28665,7 @@
       <c r="A532" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B532" s="29" t="s">
+      <c r="B532" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D532" s="1" t="s">
@@ -28723,7 +28691,7 @@
       <c r="A533" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B533" s="29" t="s">
+      <c r="B533" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D533" s="1" t="s">
@@ -28749,7 +28717,7 @@
       <c r="A534" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B534" s="29" t="s">
+      <c r="B534" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D534" s="1" t="s">
@@ -28775,7 +28743,7 @@
       <c r="A535" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B535" s="29" t="s">
+      <c r="B535" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D535" s="1" t="s">
@@ -28801,7 +28769,7 @@
       <c r="A536" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B536" s="29" t="s">
+      <c r="B536" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D536" s="1" t="s">
@@ -28827,7 +28795,7 @@
       <c r="A537" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B537" s="29" t="s">
+      <c r="B537" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D537" s="1" t="s">
@@ -28853,7 +28821,7 @@
       <c r="A538" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B538" s="29" t="s">
+      <c r="B538" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D538" s="1" t="s">
@@ -28879,7 +28847,7 @@
       <c r="A539" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B539" s="29" t="s">
+      <c r="B539" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D539" s="1" t="s">
@@ -28905,7 +28873,7 @@
       <c r="A540" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B540" s="29" t="s">
+      <c r="B540" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D540" s="1" t="s">
@@ -28931,7 +28899,7 @@
       <c r="A541" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B541" s="29" t="s">
+      <c r="B541" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D541" s="1" t="s">
@@ -28957,7 +28925,7 @@
       <c r="A542" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B542" s="29" t="s">
+      <c r="B542" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D542" s="1" t="s">
@@ -28983,7 +28951,7 @@
       <c r="A543" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B543" s="29" t="s">
+      <c r="B543" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D543" s="1" t="s">
@@ -29009,7 +28977,7 @@
       <c r="A544" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B544" s="29" t="s">
+      <c r="B544" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D544" s="1" t="s">
@@ -29035,7 +29003,7 @@
       <c r="A545" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B545" s="29" t="s">
+      <c r="B545" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D545" s="1" t="s">
@@ -29061,7 +29029,7 @@
       <c r="A546" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B546" s="29" t="s">
+      <c r="B546" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D546" s="1" t="s">
@@ -29087,7 +29055,7 @@
       <c r="A547" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B547" s="29" t="s">
+      <c r="B547" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D547" s="1" t="s">
@@ -29113,7 +29081,7 @@
       <c r="A548" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B548" s="29" t="s">
+      <c r="B548" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D548" s="1" t="s">
@@ -29139,7 +29107,7 @@
       <c r="A549" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B549" s="29" t="s">
+      <c r="B549" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D549" s="1" t="s">
@@ -29165,7 +29133,7 @@
       <c r="A550" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B550" s="29" t="s">
+      <c r="B550" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D550" s="1" t="s">
@@ -29191,7 +29159,7 @@
       <c r="A551" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B551" s="29" t="s">
+      <c r="B551" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D551" s="1" t="s">
@@ -29217,7 +29185,7 @@
       <c r="A552" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B552" s="29" t="s">
+      <c r="B552" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D552" s="1" t="s">
@@ -29243,7 +29211,7 @@
       <c r="A553" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B553" s="29" t="s">
+      <c r="B553" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D553" s="1" t="s">
@@ -29269,7 +29237,7 @@
       <c r="A554" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B554" s="29" t="s">
+      <c r="B554" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D554" s="1" t="s">
@@ -29295,7 +29263,7 @@
       <c r="A555" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B555" s="29" t="s">
+      <c r="B555" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D555" s="1" t="s">
@@ -29321,7 +29289,7 @@
       <c r="A556" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B556" s="29" t="s">
+      <c r="B556" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D556" s="1" t="s">
@@ -29347,7 +29315,7 @@
       <c r="A557" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B557" s="29" t="s">
+      <c r="B557" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D557" s="1" t="s">
@@ -29373,7 +29341,7 @@
       <c r="A558" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B558" s="29" t="s">
+      <c r="B558" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D558" s="1" t="s">
@@ -29399,7 +29367,7 @@
       <c r="A559" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B559" s="29" t="s">
+      <c r="B559" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D559" s="1" t="s">
@@ -29425,7 +29393,7 @@
       <c r="A560" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B560" s="29" t="s">
+      <c r="B560" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D560" s="1" t="s">
@@ -29451,7 +29419,7 @@
       <c r="A561" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B561" s="29" t="s">
+      <c r="B561" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D561" s="1" t="s">
@@ -29477,7 +29445,7 @@
       <c r="A562" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B562" s="29" t="s">
+      <c r="B562" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D562" s="1" t="s">
@@ -29503,7 +29471,7 @@
       <c r="A563" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B563" s="29" t="s">
+      <c r="B563" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D563" s="1" t="s">
@@ -29529,7 +29497,7 @@
       <c r="A564" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B564" s="29" t="s">
+      <c r="B564" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D564" s="1" t="s">
@@ -29555,7 +29523,7 @@
       <c r="A565" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B565" s="29" t="s">
+      <c r="B565" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D565" s="1" t="s">
@@ -29581,7 +29549,7 @@
       <c r="A566" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B566" s="29" t="s">
+      <c r="B566" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D566" s="1" t="s">
@@ -29607,7 +29575,7 @@
       <c r="A567" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B567" s="29" t="s">
+      <c r="B567" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D567" s="1" t="s">
@@ -29633,7 +29601,7 @@
       <c r="A568" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B568" s="29" t="s">
+      <c r="B568" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D568" s="1" t="s">
@@ -29659,7 +29627,7 @@
       <c r="A569" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B569" s="29" t="s">
+      <c r="B569" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D569" s="1" t="s">
@@ -29685,7 +29653,7 @@
       <c r="A570" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B570" s="29" t="s">
+      <c r="B570" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D570" s="1" t="s">
@@ -29711,7 +29679,7 @@
       <c r="A571" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B571" s="29" t="s">
+      <c r="B571" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D571" s="1" t="s">
@@ -29737,7 +29705,7 @@
       <c r="A572" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B572" s="29" t="s">
+      <c r="B572" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D572" s="1" t="s">
@@ -29763,7 +29731,7 @@
       <c r="A573" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B573" s="29" t="s">
+      <c r="B573" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D573" s="1" t="s">
@@ -29789,7 +29757,7 @@
       <c r="A574" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B574" s="29" t="s">
+      <c r="B574" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D574" s="1" t="s">
@@ -29815,7 +29783,7 @@
       <c r="A575" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B575" s="29" t="s">
+      <c r="B575" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D575" s="1" t="s">
@@ -29841,7 +29809,7 @@
       <c r="A576" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B576" s="29" t="s">
+      <c r="B576" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D576" s="1" t="s">
@@ -29867,7 +29835,7 @@
       <c r="A577" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B577" s="29" t="s">
+      <c r="B577" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D577" s="1" t="s">
@@ -29893,7 +29861,7 @@
       <c r="A578" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B578" s="29" t="s">
+      <c r="B578" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D578" s="1" t="s">
@@ -29919,7 +29887,7 @@
       <c r="A579" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B579" s="29" t="s">
+      <c r="B579" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D579" s="1" t="s">
@@ -29945,7 +29913,7 @@
       <c r="A580" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B580" s="29" t="s">
+      <c r="B580" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D580" s="1" t="s">
@@ -29971,7 +29939,7 @@
       <c r="A581" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B581" s="29" t="s">
+      <c r="B581" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D581" s="1" t="s">
@@ -29997,7 +29965,7 @@
       <c r="A582" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B582" s="29" t="s">
+      <c r="B582" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D582" s="1" t="s">
@@ -30023,7 +29991,7 @@
       <c r="A583" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B583" s="29" t="s">
+      <c r="B583" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D583" s="1" t="s">
@@ -30049,7 +30017,7 @@
       <c r="A584" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B584" s="29" t="s">
+      <c r="B584" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D584" s="1" t="s">
@@ -30075,7 +30043,7 @@
       <c r="A585" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B585" s="29" t="s">
+      <c r="B585" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D585" s="1" t="s">
@@ -30101,7 +30069,7 @@
       <c r="A586" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B586" s="29" t="s">
+      <c r="B586" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D586" s="1" t="s">
@@ -30127,7 +30095,7 @@
       <c r="A587" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B587" s="29" t="s">
+      <c r="B587" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D587" s="1" t="s">
@@ -30153,7 +30121,7 @@
       <c r="A588" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B588" s="29" t="s">
+      <c r="B588" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D588" s="1" t="s">
@@ -30179,7 +30147,7 @@
       <c r="A589" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B589" s="29" t="s">
+      <c r="B589" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D589" s="1" t="s">
@@ -30205,7 +30173,7 @@
       <c r="A590" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B590" s="29" t="s">
+      <c r="B590" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D590" s="1" t="s">
@@ -30231,7 +30199,7 @@
       <c r="A591" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B591" s="29" t="s">
+      <c r="B591" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D591" s="1" t="s">
@@ -30257,7 +30225,7 @@
       <c r="A592" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B592" s="29" t="s">
+      <c r="B592" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D592" s="1" t="s">
@@ -30283,7 +30251,7 @@
       <c r="A593" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B593" s="29" t="s">
+      <c r="B593" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D593" s="1" t="s">
@@ -30309,7 +30277,7 @@
       <c r="A594" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B594" s="29" t="s">
+      <c r="B594" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D594" s="1" t="s">
@@ -30335,7 +30303,7 @@
       <c r="A595" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B595" s="29" t="s">
+      <c r="B595" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D595" s="1" t="s">
@@ -30361,7 +30329,7 @@
       <c r="A596" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B596" s="29" t="s">
+      <c r="B596" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D596" s="1" t="s">
@@ -30387,7 +30355,7 @@
       <c r="A597" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B597" s="29" t="s">
+      <c r="B597" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D597" s="1" t="s">
@@ -30413,7 +30381,7 @@
       <c r="A598" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B598" s="29" t="s">
+      <c r="B598" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D598" s="1" t="s">
@@ -30439,7 +30407,7 @@
       <c r="A599" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B599" s="29" t="s">
+      <c r="B599" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D599" s="1" t="s">
@@ -30465,7 +30433,7 @@
       <c r="A600" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B600" s="29" t="s">
+      <c r="B600" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D600" s="1" t="s">
@@ -30491,7 +30459,7 @@
       <c r="A601" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B601" s="29" t="s">
+      <c r="B601" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D601" s="1" t="s">
@@ -30517,7 +30485,7 @@
       <c r="A602" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B602" s="29" t="s">
+      <c r="B602" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D602" s="1" t="s">
@@ -30543,7 +30511,7 @@
       <c r="A603" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B603" s="29" t="s">
+      <c r="B603" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D603" s="1" t="s">
@@ -30569,7 +30537,7 @@
       <c r="A604" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B604" s="29" t="s">
+      <c r="B604" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D604" s="1" t="s">
@@ -30595,7 +30563,7 @@
       <c r="A605" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B605" s="29" t="s">
+      <c r="B605" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D605" s="1" t="s">
@@ -30621,7 +30589,7 @@
       <c r="A606" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B606" s="29" t="s">
+      <c r="B606" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D606" s="1" t="s">
@@ -30647,7 +30615,7 @@
       <c r="A607" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B607" s="29" t="s">
+      <c r="B607" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D607" s="1" t="s">
@@ -30673,7 +30641,7 @@
       <c r="A608" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B608" s="29" t="s">
+      <c r="B608" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D608" s="1" t="s">
@@ -30699,7 +30667,7 @@
       <c r="A609" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B609" s="29" t="s">
+      <c r="B609" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D609" s="1" t="s">
@@ -30725,7 +30693,7 @@
       <c r="A610" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B610" s="29" t="s">
+      <c r="B610" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D610" s="1" t="s">
@@ -30751,7 +30719,7 @@
       <c r="A611" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B611" s="29" t="s">
+      <c r="B611" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D611" s="1" t="s">
@@ -30777,7 +30745,7 @@
       <c r="A612" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B612" s="29" t="s">
+      <c r="B612" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D612" s="1" t="s">
@@ -30803,7 +30771,7 @@
       <c r="A613" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B613" s="29" t="s">
+      <c r="B613" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D613" s="1" t="s">
@@ -30829,7 +30797,7 @@
       <c r="A614" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B614" s="29" t="s">
+      <c r="B614" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D614" s="1" t="s">
@@ -30855,7 +30823,7 @@
       <c r="A615" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B615" s="29" t="s">
+      <c r="B615" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D615" s="1" t="s">
@@ -30881,7 +30849,7 @@
       <c r="A616" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B616" s="29" t="s">
+      <c r="B616" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D616" s="1" t="s">
@@ -30907,7 +30875,7 @@
       <c r="A617" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B617" s="29" t="s">
+      <c r="B617" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D617" s="1" t="s">
@@ -30933,7 +30901,7 @@
       <c r="A618" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B618" s="29" t="s">
+      <c r="B618" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D618" s="1" t="s">
@@ -30959,7 +30927,7 @@
       <c r="A619" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B619" s="29" t="s">
+      <c r="B619" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D619" s="1" t="s">
@@ -30985,7 +30953,7 @@
       <c r="A620" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B620" s="29" t="s">
+      <c r="B620" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D620" s="1" t="s">
@@ -31011,7 +30979,7 @@
       <c r="A621" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B621" s="29" t="s">
+      <c r="B621" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D621" s="1" t="s">
@@ -31037,7 +31005,7 @@
       <c r="A622" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B622" s="29" t="s">
+      <c r="B622" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D622" s="1" t="s">
@@ -31063,7 +31031,7 @@
       <c r="A623" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B623" s="29" t="s">
+      <c r="B623" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D623" s="1" t="s">
@@ -31089,7 +31057,7 @@
       <c r="A624" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B624" s="29" t="s">
+      <c r="B624" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D624" s="1" t="s">
@@ -31115,7 +31083,7 @@
       <c r="A625" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B625" s="29" t="s">
+      <c r="B625" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D625" s="1" t="s">
@@ -31141,7 +31109,7 @@
       <c r="A626" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B626" s="29" t="s">
+      <c r="B626" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D626" s="1" t="s">
@@ -31167,7 +31135,7 @@
       <c r="A627" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B627" s="29" t="s">
+      <c r="B627" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D627" s="1" t="s">
@@ -31193,7 +31161,7 @@
       <c r="A628" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B628" s="29" t="s">
+      <c r="B628" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D628" s="1" t="s">
@@ -31219,7 +31187,7 @@
       <c r="A629" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B629" s="29" t="s">
+      <c r="B629" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D629" s="1" t="s">
@@ -31245,7 +31213,7 @@
       <c r="A630" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B630" s="29" t="s">
+      <c r="B630" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D630" s="1" t="s">
@@ -31271,7 +31239,7 @@
       <c r="A631" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B631" s="29" t="s">
+      <c r="B631" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D631" s="1" t="s">
@@ -31297,7 +31265,7 @@
       <c r="A632" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B632" s="29" t="s">
+      <c r="B632" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D632" s="1" t="s">
@@ -31323,7 +31291,7 @@
       <c r="A633" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B633" s="29" t="s">
+      <c r="B633" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D633" s="1" t="s">
@@ -31349,7 +31317,7 @@
       <c r="A634" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B634" s="29" t="s">
+      <c r="B634" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D634" s="1" t="s">
@@ -31375,7 +31343,7 @@
       <c r="A635" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B635" s="29" t="s">
+      <c r="B635" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D635" s="1" t="s">
@@ -31401,7 +31369,7 @@
       <c r="A636" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B636" s="29" t="s">
+      <c r="B636" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D636" s="1" t="s">
@@ -31427,7 +31395,7 @@
       <c r="A637" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B637" s="29" t="s">
+      <c r="B637" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D637" s="1" t="s">
@@ -31453,7 +31421,7 @@
       <c r="A638" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B638" s="29" t="s">
+      <c r="B638" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D638" s="1" t="s">
@@ -31479,7 +31447,7 @@
       <c r="A639" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B639" s="29" t="s">
+      <c r="B639" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D639" s="1" t="s">
@@ -31505,7 +31473,7 @@
       <c r="A640" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B640" s="29" t="s">
+      <c r="B640" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D640" s="1" t="s">
@@ -31531,7 +31499,7 @@
       <c r="A641" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B641" s="29" t="s">
+      <c r="B641" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D641" s="1" t="s">
@@ -31557,7 +31525,7 @@
       <c r="A642" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B642" s="29" t="s">
+      <c r="B642" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D642" s="1" t="s">
@@ -31583,7 +31551,7 @@
       <c r="A643" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B643" s="29" t="s">
+      <c r="B643" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D643" s="1" t="s">
@@ -31609,7 +31577,7 @@
       <c r="A644" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B644" s="29" t="s">
+      <c r="B644" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D644" s="1" t="s">
@@ -31635,7 +31603,7 @@
       <c r="A645" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B645" s="29" t="s">
+      <c r="B645" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D645" s="1" t="s">
@@ -31661,7 +31629,7 @@
       <c r="A646" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B646" s="29" t="s">
+      <c r="B646" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D646" s="1" t="s">
@@ -31687,7 +31655,7 @@
       <c r="A647" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B647" s="29" t="s">
+      <c r="B647" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D647" s="1" t="s">
@@ -31713,7 +31681,7 @@
       <c r="A648" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B648" s="29" t="s">
+      <c r="B648" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D648" s="1" t="s">
@@ -31739,7 +31707,7 @@
       <c r="A649" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B649" s="29" t="s">
+      <c r="B649" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D649" s="1" t="s">
@@ -31765,7 +31733,7 @@
       <c r="A650" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B650" s="29" t="s">
+      <c r="B650" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D650" s="1" t="s">
@@ -31791,7 +31759,7 @@
       <c r="A651" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B651" s="29" t="s">
+      <c r="B651" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D651" s="1" t="s">
@@ -31817,7 +31785,7 @@
       <c r="A652" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B652" s="29" t="s">
+      <c r="B652" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D652" s="1" t="s">
@@ -31843,7 +31811,7 @@
       <c r="A653" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B653" s="29" t="s">
+      <c r="B653" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D653" s="1" t="s">
@@ -31869,7 +31837,7 @@
       <c r="A654" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B654" s="29" t="s">
+      <c r="B654" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D654" s="1" t="s">
@@ -31895,7 +31863,7 @@
       <c r="A655" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B655" s="29" t="s">
+      <c r="B655" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D655" s="1" t="s">
@@ -31921,7 +31889,7 @@
       <c r="A656" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B656" s="29" t="s">
+      <c r="B656" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D656" s="1" t="s">
@@ -31947,7 +31915,7 @@
       <c r="A657" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B657" s="29" t="s">
+      <c r="B657" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D657" s="1" t="s">
@@ -31973,7 +31941,7 @@
       <c r="A658" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B658" s="29" t="s">
+      <c r="B658" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D658" s="1" t="s">
@@ -31999,7 +31967,7 @@
       <c r="A659" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B659" s="29" t="s">
+      <c r="B659" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D659" s="1" t="s">
@@ -32025,7 +31993,7 @@
       <c r="A660" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B660" s="29" t="s">
+      <c r="B660" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D660" s="1" t="s">
@@ -32051,7 +32019,7 @@
       <c r="A661" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B661" s="29" t="s">
+      <c r="B661" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D661" s="1" t="s">
@@ -32077,7 +32045,7 @@
       <c r="A662" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B662" s="29" t="s">
+      <c r="B662" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D662" s="1" t="s">
@@ -32103,7 +32071,7 @@
       <c r="A663" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B663" s="29" t="s">
+      <c r="B663" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D663" s="1" t="s">
@@ -32129,7 +32097,7 @@
       <c r="A664" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B664" s="29" t="s">
+      <c r="B664" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D664" s="1" t="s">
@@ -32155,7 +32123,7 @@
       <c r="A665" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B665" s="29" t="s">
+      <c r="B665" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D665" s="1" t="s">
@@ -32181,7 +32149,7 @@
       <c r="A666" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B666" s="29" t="s">
+      <c r="B666" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D666" s="1" t="s">
@@ -32207,7 +32175,7 @@
       <c r="A667" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B667" s="29" t="s">
+      <c r="B667" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D667" s="1" t="s">
@@ -32233,7 +32201,7 @@
       <c r="A668" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B668" s="29" t="s">
+      <c r="B668" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D668" s="1" t="s">
@@ -32259,7 +32227,7 @@
       <c r="A669" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B669" s="29" t="s">
+      <c r="B669" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D669" s="1" t="s">
@@ -32285,7 +32253,7 @@
       <c r="A670" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B670" s="29" t="s">
+      <c r="B670" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D670" s="1" t="s">
@@ -32311,7 +32279,7 @@
       <c r="A671" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B671" s="29" t="s">
+      <c r="B671" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D671" s="1" t="s">
@@ -32337,7 +32305,7 @@
       <c r="A672" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B672" s="29" t="s">
+      <c r="B672" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D672" s="1" t="s">
@@ -32363,7 +32331,7 @@
       <c r="A673" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B673" s="29" t="s">
+      <c r="B673" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D673" s="1" t="s">
@@ -32389,7 +32357,7 @@
       <c r="A674" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B674" s="29" t="s">
+      <c r="B674" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D674" s="1" t="s">
@@ -32415,7 +32383,7 @@
       <c r="A675" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B675" s="29" t="s">
+      <c r="B675" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D675" s="1" t="s">
@@ -32441,7 +32409,7 @@
       <c r="A676" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B676" s="29" t="s">
+      <c r="B676" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D676" s="1" t="s">
@@ -32467,7 +32435,7 @@
       <c r="A677" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B677" s="29" t="s">
+      <c r="B677" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D677" s="1" t="s">
@@ -32493,7 +32461,7 @@
       <c r="A678" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B678" s="29" t="s">
+      <c r="B678" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D678" s="1" t="s">
@@ -32519,7 +32487,7 @@
       <c r="A679" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B679" s="29" t="s">
+      <c r="B679" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D679" s="1" t="s">
@@ -32545,7 +32513,7 @@
       <c r="A680" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B680" s="29" t="s">
+      <c r="B680" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D680" s="1" t="s">
@@ -32571,7 +32539,7 @@
       <c r="A681" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B681" s="29" t="s">
+      <c r="B681" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D681" s="1" t="s">
@@ -32597,7 +32565,7 @@
       <c r="A682" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B682" s="29" t="s">
+      <c r="B682" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D682" s="1" t="s">
@@ -32623,7 +32591,7 @@
       <c r="A683" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B683" s="29" t="s">
+      <c r="B683" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D683" s="1" t="s">
@@ -32649,7 +32617,7 @@
       <c r="A684" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B684" s="29" t="s">
+      <c r="B684" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D684" s="1" t="s">
@@ -32675,7 +32643,7 @@
       <c r="A685" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B685" s="29" t="s">
+      <c r="B685" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D685" s="1" t="s">
@@ -32701,7 +32669,7 @@
       <c r="A686" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B686" s="29" t="s">
+      <c r="B686" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D686" s="1" t="s">
@@ -32727,7 +32695,7 @@
       <c r="A687" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B687" s="29" t="s">
+      <c r="B687" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D687" s="1" t="s">
@@ -32753,7 +32721,7 @@
       <c r="A688" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B688" s="29" t="s">
+      <c r="B688" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D688" s="1" t="s">
@@ -32779,7 +32747,7 @@
       <c r="A689" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B689" s="29" t="s">
+      <c r="B689" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D689" s="1" t="s">
@@ -32805,7 +32773,7 @@
       <c r="A690" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B690" s="29" t="s">
+      <c r="B690" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D690" s="1" t="s">
@@ -32831,7 +32799,7 @@
       <c r="A691" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B691" s="29" t="s">
+      <c r="B691" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D691" s="1" t="s">
@@ -32857,7 +32825,7 @@
       <c r="A692" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B692" s="29" t="s">
+      <c r="B692" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D692" s="1" t="s">
@@ -32883,7 +32851,7 @@
       <c r="A693" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B693" s="29" t="s">
+      <c r="B693" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D693" s="1" t="s">
@@ -32909,7 +32877,7 @@
       <c r="A694" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B694" s="29" t="s">
+      <c r="B694" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D694" s="1" t="s">
@@ -32935,7 +32903,7 @@
       <c r="A695" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B695" s="29" t="s">
+      <c r="B695" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D695" s="1" t="s">
@@ -32961,7 +32929,7 @@
       <c r="A696" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B696" s="29" t="s">
+      <c r="B696" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D696" s="1" t="s">
@@ -32987,7 +32955,7 @@
       <c r="A697" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B697" s="29" t="s">
+      <c r="B697" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D697" s="1" t="s">
@@ -33013,7 +32981,7 @@
       <c r="A698" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B698" s="29" t="s">
+      <c r="B698" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D698" s="1" t="s">
@@ -33039,7 +33007,7 @@
       <c r="A699" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B699" s="29" t="s">
+      <c r="B699" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D699" s="1" t="s">
@@ -33065,7 +33033,7 @@
       <c r="A700" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B700" s="29" t="s">
+      <c r="B700" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D700" s="1" t="s">
@@ -33091,7 +33059,7 @@
       <c r="A701" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B701" s="29" t="s">
+      <c r="B701" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D701" s="1" t="s">
@@ -33117,7 +33085,7 @@
       <c r="A702" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B702" s="29" t="s">
+      <c r="B702" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D702" s="1" t="s">
@@ -33143,7 +33111,7 @@
       <c r="A703" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B703" s="29" t="s">
+      <c r="B703" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D703" s="1" t="s">
@@ -33169,7 +33137,7 @@
       <c r="A704" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B704" s="29" t="s">
+      <c r="B704" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D704" s="1" t="s">
@@ -33195,7 +33163,7 @@
       <c r="A705" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B705" s="29" t="s">
+      <c r="B705" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D705" s="1" t="s">
@@ -33221,7 +33189,7 @@
       <c r="A706" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B706" s="29" t="s">
+      <c r="B706" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D706" s="1" t="s">
@@ -33247,7 +33215,7 @@
       <c r="A707" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B707" s="29" t="s">
+      <c r="B707" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D707" s="1" t="s">
@@ -33273,7 +33241,7 @@
       <c r="A708" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B708" s="29" t="s">
+      <c r="B708" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D708" s="1" t="s">
@@ -33299,7 +33267,7 @@
       <c r="A709" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B709" s="29" t="s">
+      <c r="B709" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D709" s="1" t="s">
@@ -33325,7 +33293,7 @@
       <c r="A710" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B710" s="29" t="s">
+      <c r="B710" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D710" s="1" t="s">
@@ -33351,7 +33319,7 @@
       <c r="A711" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B711" s="29" t="s">
+      <c r="B711" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D711" s="1" t="s">
@@ -33377,7 +33345,7 @@
       <c r="A712" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B712" s="29" t="s">
+      <c r="B712" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D712" s="1" t="s">
@@ -33403,7 +33371,7 @@
       <c r="A713" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B713" s="29" t="s">
+      <c r="B713" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D713" s="1" t="s">
@@ -33429,7 +33397,7 @@
       <c r="A714" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B714" s="29" t="s">
+      <c r="B714" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D714" s="1" t="s">
@@ -33455,7 +33423,7 @@
       <c r="A715" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B715" s="29" t="s">
+      <c r="B715" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D715" s="1" t="s">
@@ -33481,7 +33449,7 @@
       <c r="A716" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B716" s="29" t="s">
+      <c r="B716" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D716" s="1" t="s">
@@ -33507,7 +33475,7 @@
       <c r="A717" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B717" s="29" t="s">
+      <c r="B717" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D717" s="1" t="s">
@@ -33533,7 +33501,7 @@
       <c r="A718" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B718" s="29" t="s">
+      <c r="B718" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D718" s="1" t="s">
@@ -33559,7 +33527,7 @@
       <c r="A719" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B719" s="29" t="s">
+      <c r="B719" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D719" s="1" t="s">
@@ -33585,7 +33553,7 @@
       <c r="A720" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B720" s="29" t="s">
+      <c r="B720" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D720" s="1" t="s">
@@ -33611,7 +33579,7 @@
       <c r="A721" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B721" s="29" t="s">
+      <c r="B721" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D721" s="1" t="s">
@@ -33637,7 +33605,7 @@
       <c r="A722" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B722" s="29" t="s">
+      <c r="B722" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D722" s="1" t="s">
@@ -33663,7 +33631,7 @@
       <c r="A723" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B723" s="29" t="s">
+      <c r="B723" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D723" s="1" t="s">
@@ -33689,7 +33657,7 @@
       <c r="A724" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B724" s="29" t="s">
+      <c r="B724" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D724" s="1" t="s">
@@ -33715,7 +33683,7 @@
       <c r="A725" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B725" s="29" t="s">
+      <c r="B725" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D725" s="1" t="s">
@@ -33741,7 +33709,7 @@
       <c r="A726" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B726" s="29" t="s">
+      <c r="B726" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D726" s="1" t="s">
@@ -33767,7 +33735,7 @@
       <c r="A727" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B727" s="29" t="s">
+      <c r="B727" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D727" s="1" t="s">
@@ -33793,7 +33761,7 @@
       <c r="A728" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B728" s="29" t="s">
+      <c r="B728" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D728" s="1" t="s">
@@ -33819,7 +33787,7 @@
       <c r="A729" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B729" s="29" t="s">
+      <c r="B729" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D729" s="1" t="s">
@@ -33845,7 +33813,7 @@
       <c r="A730" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B730" s="29" t="s">
+      <c r="B730" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D730" s="1" t="s">
@@ -33871,7 +33839,7 @@
       <c r="A731" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B731" s="29" t="s">
+      <c r="B731" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D731" s="1" t="s">
@@ -33897,7 +33865,7 @@
       <c r="A732" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B732" s="29" t="s">
+      <c r="B732" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D732" s="1" t="s">
@@ -33923,7 +33891,7 @@
       <c r="A733" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B733" s="29" t="s">
+      <c r="B733" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D733" s="1" t="s">
@@ -33949,7 +33917,7 @@
       <c r="A734" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B734" s="29" t="s">
+      <c r="B734" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D734" s="1" t="s">
@@ -33975,7 +33943,7 @@
       <c r="A735" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B735" s="29" t="s">
+      <c r="B735" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D735" s="1" t="s">
@@ -34001,7 +33969,7 @@
       <c r="A736" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B736" s="29" t="s">
+      <c r="B736" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D736" s="1" t="s">
@@ -34027,7 +33995,7 @@
       <c r="A737" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B737" s="29" t="s">
+      <c r="B737" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D737" s="1" t="s">
@@ -34053,7 +34021,7 @@
       <c r="A738" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B738" s="29" t="s">
+      <c r="B738" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D738" s="1" t="s">
@@ -34079,7 +34047,7 @@
       <c r="A739" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B739" s="29" t="s">
+      <c r="B739" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D739" s="1" t="s">
@@ -34105,7 +34073,7 @@
       <c r="A740" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B740" s="29" t="s">
+      <c r="B740" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D740" s="1" t="s">
@@ -34131,7 +34099,7 @@
       <c r="A741" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B741" s="29" t="s">
+      <c r="B741" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D741" s="1" t="s">
@@ -34157,7 +34125,7 @@
       <c r="A742" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B742" s="29" t="s">
+      <c r="B742" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D742" s="1" t="s">
@@ -34183,7 +34151,7 @@
       <c r="A743" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B743" s="29" t="s">
+      <c r="B743" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D743" s="1" t="s">
@@ -34209,7 +34177,7 @@
       <c r="A744" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B744" s="29" t="s">
+      <c r="B744" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D744" s="1" t="s">
@@ -34235,7 +34203,7 @@
       <c r="A745" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B745" s="29" t="s">
+      <c r="B745" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D745" s="1" t="s">
@@ -34261,7 +34229,7 @@
       <c r="A746" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B746" s="29" t="s">
+      <c r="B746" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D746" s="1" t="s">
@@ -34287,7 +34255,7 @@
       <c r="A747" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B747" s="29" t="s">
+      <c r="B747" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D747" s="1" t="s">
@@ -34313,7 +34281,7 @@
       <c r="A748" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B748" s="29" t="s">
+      <c r="B748" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D748" s="1" t="s">
@@ -34339,7 +34307,7 @@
       <c r="A749" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B749" s="29" t="s">
+      <c r="B749" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D749" s="1" t="s">
@@ -34365,7 +34333,7 @@
       <c r="A750" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B750" s="29" t="s">
+      <c r="B750" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D750" s="1" t="s">
@@ -34391,7 +34359,7 @@
       <c r="A751" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B751" s="29" t="s">
+      <c r="B751" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D751" s="1" t="s">
@@ -34417,7 +34385,7 @@
       <c r="A752" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B752" s="29" t="s">
+      <c r="B752" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D752" s="1" t="s">
@@ -34443,7 +34411,7 @@
       <c r="A753" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B753" s="29" t="s">
+      <c r="B753" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D753" s="1" t="s">
@@ -34469,7 +34437,7 @@
       <c r="A754" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B754" s="29" t="s">
+      <c r="B754" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D754" s="1" t="s">
@@ -34495,7 +34463,7 @@
       <c r="A755" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B755" s="29" t="s">
+      <c r="B755" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D755" s="1" t="s">
@@ -34521,7 +34489,7 @@
       <c r="A756" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B756" s="29" t="s">
+      <c r="B756" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D756" s="1" t="s">
@@ -34547,7 +34515,7 @@
       <c r="A757" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B757" s="29" t="s">
+      <c r="B757" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D757" s="1" t="s">
@@ -34573,7 +34541,7 @@
       <c r="A758" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B758" s="29" t="s">
+      <c r="B758" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D758" s="1" t="s">
@@ -34599,7 +34567,7 @@
       <c r="A759" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B759" s="29" t="s">
+      <c r="B759" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D759" s="1" t="s">
@@ -34625,7 +34593,7 @@
       <c r="A760" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B760" s="29" t="s">
+      <c r="B760" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D760" s="1" t="s">
@@ -34651,7 +34619,7 @@
       <c r="A761" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B761" s="29" t="s">
+      <c r="B761" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D761" s="1" t="s">
@@ -34677,7 +34645,7 @@
       <c r="A762" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B762" s="29" t="s">
+      <c r="B762" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D762" s="1" t="s">
@@ -34703,7 +34671,7 @@
       <c r="A763" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B763" s="29" t="s">
+      <c r="B763" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D763" s="1" t="s">
@@ -34729,7 +34697,7 @@
       <c r="A764" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B764" s="29" t="s">
+      <c r="B764" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D764" s="1" t="s">
@@ -34755,7 +34723,7 @@
       <c r="A765" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B765" s="29" t="s">
+      <c r="B765" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D765" s="1" t="s">
@@ -34781,7 +34749,7 @@
       <c r="A766" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B766" s="29" t="s">
+      <c r="B766" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D766" s="1" t="s">
@@ -34807,7 +34775,7 @@
       <c r="A767" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B767" s="29" t="s">
+      <c r="B767" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D767" s="1" t="s">
@@ -34833,7 +34801,7 @@
       <c r="A768" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B768" s="29" t="s">
+      <c r="B768" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D768" s="1" t="s">
@@ -34859,7 +34827,7 @@
       <c r="A769" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B769" s="29" t="s">
+      <c r="B769" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D769" s="1" t="s">
@@ -34885,7 +34853,7 @@
       <c r="A770" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B770" s="29" t="s">
+      <c r="B770" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D770" s="1" t="s">
@@ -34911,7 +34879,7 @@
       <c r="A771" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B771" s="29" t="s">
+      <c r="B771" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D771" s="1" t="s">
@@ -34937,7 +34905,7 @@
       <c r="A772" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B772" s="29" t="s">
+      <c r="B772" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D772" s="1" t="s">
@@ -34963,7 +34931,7 @@
       <c r="A773" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B773" s="29" t="s">
+      <c r="B773" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D773" s="1" t="s">
@@ -34989,7 +34957,7 @@
       <c r="A774" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B774" s="29" t="s">
+      <c r="B774" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D774" s="1" t="s">
@@ -35015,7 +34983,7 @@
       <c r="A775" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B775" s="29" t="s">
+      <c r="B775" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D775" s="1" t="s">
@@ -35041,7 +35009,7 @@
       <c r="A776" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B776" s="29" t="s">
+      <c r="B776" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D776" s="1" t="s">
@@ -35067,7 +35035,7 @@
       <c r="A777" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B777" s="29" t="s">
+      <c r="B777" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D777" s="1" t="s">
@@ -35093,7 +35061,7 @@
       <c r="A778" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B778" s="29" t="s">
+      <c r="B778" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D778" s="1" t="s">
@@ -35119,7 +35087,7 @@
       <c r="A779" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B779" s="29" t="s">
+      <c r="B779" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D779" s="1" t="s">
@@ -35145,7 +35113,7 @@
       <c r="A780" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B780" s="29" t="s">
+      <c r="B780" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D780" s="1" t="s">
@@ -35171,7 +35139,7 @@
       <c r="A781" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B781" s="29" t="s">
+      <c r="B781" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D781" s="1" t="s">
@@ -35197,7 +35165,7 @@
       <c r="A782" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B782" s="29" t="s">
+      <c r="B782" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D782" s="1" t="s">
@@ -35223,7 +35191,7 @@
       <c r="A783" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B783" s="29" t="s">
+      <c r="B783" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D783" s="1" t="s">
@@ -35249,7 +35217,7 @@
       <c r="A784" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B784" s="29" t="s">
+      <c r="B784" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D784" s="1" t="s">
@@ -35275,7 +35243,7 @@
       <c r="A785" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B785" s="29" t="s">
+      <c r="B785" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D785" s="1" t="s">
@@ -35301,7 +35269,7 @@
       <c r="A786" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B786" s="29" t="s">
+      <c r="B786" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D786" s="1" t="s">
@@ -35327,7 +35295,7 @@
       <c r="A787" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B787" s="29" t="s">
+      <c r="B787" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D787" s="1" t="s">
@@ -35353,7 +35321,7 @@
       <c r="A788" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B788" s="29" t="s">
+      <c r="B788" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D788" s="1" t="s">
@@ -35379,7 +35347,7 @@
       <c r="A789" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B789" s="29" t="s">
+      <c r="B789" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D789" s="1" t="s">
@@ -35405,7 +35373,7 @@
       <c r="A790" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B790" s="29" t="s">
+      <c r="B790" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D790" s="1" t="s">
@@ -35431,7 +35399,7 @@
       <c r="A791" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B791" s="29" t="s">
+      <c r="B791" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D791" s="1" t="s">
@@ -35457,7 +35425,7 @@
       <c r="A792" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B792" s="29" t="s">
+      <c r="B792" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D792" s="1" t="s">
@@ -35483,7 +35451,7 @@
       <c r="A793" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B793" s="29" t="s">
+      <c r="B793" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D793" s="1" t="s">
@@ -35509,7 +35477,7 @@
       <c r="A794" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B794" s="29" t="s">
+      <c r="B794" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D794" s="1" t="s">
@@ -35535,7 +35503,7 @@
       <c r="A795" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B795" s="29" t="s">
+      <c r="B795" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D795" s="1" t="s">
@@ -35561,7 +35529,7 @@
       <c r="A796" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B796" s="29" t="s">
+      <c r="B796" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D796" s="1" t="s">
@@ -35587,7 +35555,7 @@
       <c r="A797" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B797" s="29" t="s">
+      <c r="B797" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D797" s="1" t="s">
@@ -35613,7 +35581,7 @@
       <c r="A798" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B798" s="29" t="s">
+      <c r="B798" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D798" s="1" t="s">
@@ -35639,7 +35607,7 @@
       <c r="A799" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B799" s="29" t="s">
+      <c r="B799" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D799" s="1" t="s">
@@ -35665,7 +35633,7 @@
       <c r="A800" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B800" s="29" t="s">
+      <c r="B800" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D800" s="1" t="s">
@@ -35691,7 +35659,7 @@
       <c r="A801" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B801" s="29" t="s">
+      <c r="B801" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D801" s="1" t="s">
@@ -35717,7 +35685,7 @@
       <c r="A802" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B802" s="29" t="s">
+      <c r="B802" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D802" s="1" t="s">
@@ -35743,7 +35711,7 @@
       <c r="A803" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B803" s="29" t="s">
+      <c r="B803" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D803" s="1" t="s">
@@ -35769,7 +35737,7 @@
       <c r="A804" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B804" s="29" t="s">
+      <c r="B804" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D804" s="1" t="s">
@@ -35795,7 +35763,7 @@
       <c r="A805" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B805" s="29" t="s">
+      <c r="B805" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D805" s="1" t="s">
@@ -35821,7 +35789,7 @@
       <c r="A806" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B806" s="29" t="s">
+      <c r="B806" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D806" s="1" t="s">
@@ -35847,7 +35815,7 @@
       <c r="A807" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B807" s="29" t="s">
+      <c r="B807" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D807" s="1" t="s">
@@ -35873,7 +35841,7 @@
       <c r="A808" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B808" s="29" t="s">
+      <c r="B808" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D808" s="1" t="s">
@@ -35899,7 +35867,7 @@
       <c r="A809" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B809" s="29" t="s">
+      <c r="B809" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D809" s="1" t="s">
@@ -35925,7 +35893,7 @@
       <c r="A810" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B810" s="29" t="s">
+      <c r="B810" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D810" s="1" t="s">
@@ -35951,7 +35919,7 @@
       <c r="A811" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B811" s="29" t="s">
+      <c r="B811" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D811" s="1" t="s">
@@ -35977,7 +35945,7 @@
       <c r="A812" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B812" s="29" t="s">
+      <c r="B812" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D812" s="1" t="s">
@@ -36003,7 +35971,7 @@
       <c r="A813" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B813" s="29" t="s">
+      <c r="B813" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D813" s="1" t="s">
@@ -36029,7 +35997,7 @@
       <c r="A814" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B814" s="29" t="s">
+      <c r="B814" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D814" s="1" t="s">
@@ -36055,7 +36023,7 @@
       <c r="A815" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B815" s="29" t="s">
+      <c r="B815" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D815" s="1" t="s">
@@ -36081,7 +36049,7 @@
       <c r="A816" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B816" s="29" t="s">
+      <c r="B816" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D816" s="1" t="s">
@@ -36107,7 +36075,7 @@
       <c r="A817" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B817" s="29" t="s">
+      <c r="B817" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D817" s="1" t="s">
@@ -36133,7 +36101,7 @@
       <c r="A818" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B818" s="29" t="s">
+      <c r="B818" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D818" s="1" t="s">
@@ -36159,7 +36127,7 @@
       <c r="A819" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B819" s="29" t="s">
+      <c r="B819" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D819" s="1" t="s">
@@ -36185,7 +36153,7 @@
       <c r="A820" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B820" s="29" t="s">
+      <c r="B820" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D820" s="1" t="s">
@@ -36211,7 +36179,7 @@
       <c r="A821" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B821" s="29" t="s">
+      <c r="B821" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D821" s="1" t="s">
@@ -36237,7 +36205,7 @@
       <c r="A822" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B822" s="29" t="s">
+      <c r="B822" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D822" s="1" t="s">
@@ -36263,7 +36231,7 @@
       <c r="A823" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B823" s="29" t="s">
+      <c r="B823" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D823" s="1" t="s">
@@ -36289,7 +36257,7 @@
       <c r="A824" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B824" s="29" t="s">
+      <c r="B824" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D824" s="1" t="s">
@@ -36315,7 +36283,7 @@
       <c r="A825" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B825" s="29" t="s">
+      <c r="B825" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D825" s="1" t="s">
@@ -36341,7 +36309,7 @@
       <c r="A826" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B826" s="29" t="s">
+      <c r="B826" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D826" s="1" t="s">
@@ -36367,7 +36335,7 @@
       <c r="A827" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B827" s="29" t="s">
+      <c r="B827" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D827" s="1" t="s">
@@ -36393,7 +36361,7 @@
       <c r="A828" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B828" s="29" t="s">
+      <c r="B828" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D828" s="1" t="s">
@@ -36419,7 +36387,7 @@
       <c r="A829" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B829" s="29" t="s">
+      <c r="B829" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D829" s="1" t="s">
@@ -36445,7 +36413,7 @@
       <c r="A830" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B830" s="29" t="s">
+      <c r="B830" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D830" s="1" t="s">
@@ -36471,7 +36439,7 @@
       <c r="A831" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B831" s="29" t="s">
+      <c r="B831" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D831" s="1" t="s">
@@ -36497,7 +36465,7 @@
       <c r="A832" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B832" s="29" t="s">
+      <c r="B832" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D832" s="1" t="s">
@@ -36523,7 +36491,7 @@
       <c r="A833" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B833" s="29" t="s">
+      <c r="B833" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D833" s="1" t="s">
@@ -36549,7 +36517,7 @@
       <c r="A834" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B834" s="29" t="s">
+      <c r="B834" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D834" s="1" t="s">
@@ -36575,7 +36543,7 @@
       <c r="A835" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B835" s="29" t="s">
+      <c r="B835" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D835" s="1" t="s">
@@ -36601,7 +36569,7 @@
       <c r="A836" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B836" s="29" t="s">
+      <c r="B836" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D836" s="1" t="s">
@@ -36627,7 +36595,7 @@
       <c r="A837" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B837" s="29" t="s">
+      <c r="B837" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D837" s="1" t="s">
@@ -36653,7 +36621,7 @@
       <c r="A838" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B838" s="29" t="s">
+      <c r="B838" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D838" s="1" t="s">
@@ -36679,7 +36647,7 @@
       <c r="A839" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B839" s="29" t="s">
+      <c r="B839" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D839" s="1" t="s">
@@ -36705,7 +36673,7 @@
       <c r="A840" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B840" s="29" t="s">
+      <c r="B840" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D840" s="1" t="s">
@@ -36731,7 +36699,7 @@
       <c r="A841" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B841" s="29" t="s">
+      <c r="B841" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D841" s="1" t="s">
@@ -36757,7 +36725,7 @@
       <c r="A842" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B842" s="29" t="s">
+      <c r="B842" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D842" s="1" t="s">
@@ -36783,7 +36751,7 @@
       <c r="A843" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B843" s="29" t="s">
+      <c r="B843" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D843" s="1" t="s">
@@ -36809,7 +36777,7 @@
       <c r="A844" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B844" s="29" t="s">
+      <c r="B844" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D844" s="1" t="s">
@@ -36835,7 +36803,7 @@
       <c r="A845" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B845" s="29" t="s">
+      <c r="B845" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D845" s="1" t="s">
@@ -36861,7 +36829,7 @@
       <c r="A846" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B846" s="29" t="s">
+      <c r="B846" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D846" s="1" t="s">
@@ -36887,7 +36855,7 @@
       <c r="A847" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B847" s="29" t="s">
+      <c r="B847" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D847" s="1" t="s">
@@ -36913,7 +36881,7 @@
       <c r="A848" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B848" s="29" t="s">
+      <c r="B848" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D848" s="1" t="s">
@@ -36939,7 +36907,7 @@
       <c r="A849" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B849" s="29" t="s">
+      <c r="B849" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D849" s="1" t="s">
@@ -36965,7 +36933,7 @@
       <c r="A850" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B850" s="29" t="s">
+      <c r="B850" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D850" s="1" t="s">
@@ -36991,7 +36959,7 @@
       <c r="A851" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B851" s="29" t="s">
+      <c r="B851" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D851" s="1" t="s">
@@ -37017,7 +36985,7 @@
       <c r="A852" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B852" s="29" t="s">
+      <c r="B852" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D852" s="1" t="s">
@@ -37043,7 +37011,7 @@
       <c r="A853" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B853" s="29" t="s">
+      <c r="B853" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D853" s="1" t="s">
@@ -37069,7 +37037,7 @@
       <c r="A854" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B854" s="29" t="s">
+      <c r="B854" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D854" s="1" t="s">
@@ -37095,7 +37063,7 @@
       <c r="A855" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B855" s="29" t="s">
+      <c r="B855" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D855" s="1" t="s">
@@ -37121,7 +37089,7 @@
       <c r="A856" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B856" s="29" t="s">
+      <c r="B856" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D856" s="1" t="s">
@@ -37147,7 +37115,7 @@
       <c r="A857" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B857" s="29" t="s">
+      <c r="B857" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D857" s="1" t="s">
@@ -37173,7 +37141,7 @@
       <c r="A858" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B858" s="29" t="s">
+      <c r="B858" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D858" s="1" t="s">
@@ -37199,7 +37167,7 @@
       <c r="A859" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B859" s="29" t="s">
+      <c r="B859" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D859" s="1" t="s">
@@ -37225,7 +37193,7 @@
       <c r="A860" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B860" s="29" t="s">
+      <c r="B860" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D860" s="1" t="s">
@@ -37251,7 +37219,7 @@
       <c r="A861" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B861" s="29" t="s">
+      <c r="B861" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D861" s="1" t="s">
@@ -37277,7 +37245,7 @@
       <c r="A862" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B862" s="29" t="s">
+      <c r="B862" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D862" s="1" t="s">
@@ -37303,7 +37271,7 @@
       <c r="A863" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B863" s="29" t="s">
+      <c r="B863" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D863" s="1" t="s">
@@ -37329,7 +37297,7 @@
       <c r="A864" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B864" s="29" t="s">
+      <c r="B864" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D864" s="1" t="s">
@@ -37355,7 +37323,7 @@
       <c r="A865" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B865" s="29" t="s">
+      <c r="B865" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D865" s="1" t="s">
@@ -37381,7 +37349,7 @@
       <c r="A866" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B866" s="29" t="s">
+      <c r="B866" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D866" s="1" t="s">
@@ -37407,7 +37375,7 @@
       <c r="A867" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B867" s="29" t="s">
+      <c r="B867" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D867" s="1" t="s">
@@ -37433,7 +37401,7 @@
       <c r="A868" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B868" s="29" t="s">
+      <c r="B868" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D868" s="1" t="s">
@@ -37459,7 +37427,7 @@
       <c r="A869" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B869" s="29" t="s">
+      <c r="B869" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D869" s="1" t="s">
@@ -37485,7 +37453,7 @@
       <c r="A870" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B870" s="29" t="s">
+      <c r="B870" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D870" s="1" t="s">
@@ -37511,7 +37479,7 @@
       <c r="A871" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B871" s="29" t="s">
+      <c r="B871" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D871" s="1" t="s">
@@ -37537,7 +37505,7 @@
       <c r="A872" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B872" s="29" t="s">
+      <c r="B872" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D872" s="1" t="s">
@@ -37563,7 +37531,7 @@
       <c r="A873" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B873" s="29" t="s">
+      <c r="B873" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D873" s="1" t="s">
@@ -37589,7 +37557,7 @@
       <c r="A874" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B874" s="29" t="s">
+      <c r="B874" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D874" s="1" t="s">
@@ -37615,7 +37583,7 @@
       <c r="A875" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B875" s="29" t="s">
+      <c r="B875" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D875" s="1" t="s">
@@ -37641,7 +37609,7 @@
       <c r="A876" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B876" s="29" t="s">
+      <c r="B876" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D876" s="1" t="s">
@@ -37667,7 +37635,7 @@
       <c r="A877" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B877" s="29" t="s">
+      <c r="B877" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D877" s="1" t="s">
@@ -37693,7 +37661,7 @@
       <c r="A878" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B878" s="29" t="s">
+      <c r="B878" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D878" s="1" t="s">
@@ -37719,7 +37687,7 @@
       <c r="A879" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B879" s="29" t="s">
+      <c r="B879" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D879" s="1" t="s">
@@ -37745,7 +37713,7 @@
       <c r="A880" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B880" s="29" t="s">
+      <c r="B880" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D880" s="1" t="s">
@@ -37771,7 +37739,7 @@
       <c r="A881" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B881" s="29" t="s">
+      <c r="B881" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D881" s="1" t="s">
@@ -37797,7 +37765,7 @@
       <c r="A882" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B882" s="29" t="s">
+      <c r="B882" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D882" s="1" t="s">
@@ -37823,7 +37791,7 @@
       <c r="A883" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B883" s="29" t="s">
+      <c r="B883" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D883" s="1" t="s">
@@ -37849,7 +37817,7 @@
       <c r="A884" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B884" s="29" t="s">
+      <c r="B884" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D884" s="1" t="s">
@@ -37875,7 +37843,7 @@
       <c r="A885" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B885" s="29" t="s">
+      <c r="B885" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D885" s="1" t="s">
@@ -37901,7 +37869,7 @@
       <c r="A886" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B886" s="29" t="s">
+      <c r="B886" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D886" s="1" t="s">
@@ -37927,7 +37895,7 @@
       <c r="A887" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B887" s="29" t="s">
+      <c r="B887" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D887" s="1" t="s">
@@ -37953,7 +37921,7 @@
       <c r="A888" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B888" s="29" t="s">
+      <c r="B888" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D888" s="1" t="s">
@@ -37979,7 +37947,7 @@
       <c r="A889" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B889" s="29" t="s">
+      <c r="B889" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D889" s="1" t="s">
@@ -38005,7 +37973,7 @@
       <c r="A890" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B890" s="29" t="s">
+      <c r="B890" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D890" s="1" t="s">
@@ -38031,7 +37999,7 @@
       <c r="A891" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B891" s="29" t="s">
+      <c r="B891" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D891" s="1" t="s">
@@ -38057,7 +38025,7 @@
       <c r="A892" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B892" s="29" t="s">
+      <c r="B892" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D892" s="1" t="s">
@@ -38083,7 +38051,7 @@
       <c r="A893" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B893" s="29" t="s">
+      <c r="B893" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D893" s="1" t="s">
@@ -38109,7 +38077,7 @@
       <c r="A894" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B894" s="29" t="s">
+      <c r="B894" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D894" s="1" t="s">
@@ -38135,7 +38103,7 @@
       <c r="A895" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B895" s="29" t="s">
+      <c r="B895" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D895" s="1" t="s">
@@ -38161,7 +38129,7 @@
       <c r="A896" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B896" s="29" t="s">
+      <c r="B896" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D896" s="1" t="s">
@@ -38187,7 +38155,7 @@
       <c r="A897" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B897" s="29" t="s">
+      <c r="B897" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D897" s="1" t="s">
@@ -38213,7 +38181,7 @@
       <c r="A898" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B898" s="29" t="s">
+      <c r="B898" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D898" s="1" t="s">
@@ -38239,7 +38207,7 @@
       <c r="A899" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B899" s="29" t="s">
+      <c r="B899" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D899" s="1" t="s">
@@ -38265,7 +38233,7 @@
       <c r="A900" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B900" s="29" t="s">
+      <c r="B900" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D900" s="1" t="s">
@@ -38291,7 +38259,7 @@
       <c r="A901" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B901" s="29" t="s">
+      <c r="B901" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D901" s="1" t="s">
@@ -38317,7 +38285,7 @@
       <c r="A902" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B902" s="29" t="s">
+      <c r="B902" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D902" s="1" t="s">
@@ -38343,7 +38311,7 @@
       <c r="A903" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B903" s="29" t="s">
+      <c r="B903" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D903" s="1" t="s">
@@ -38369,7 +38337,7 @@
       <c r="A904" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B904" s="29" t="s">
+      <c r="B904" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D904" s="1" t="s">
@@ -38395,7 +38363,7 @@
       <c r="A905" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B905" s="29" t="s">
+      <c r="B905" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D905" s="1" t="s">
@@ -38421,7 +38389,7 @@
       <c r="A906" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B906" s="29" t="s">
+      <c r="B906" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D906" s="1" t="s">
@@ -38447,7 +38415,7 @@
       <c r="A907" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B907" s="29" t="s">
+      <c r="B907" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D907" s="1" t="s">
@@ -38473,7 +38441,7 @@
       <c r="A908" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B908" s="29" t="s">
+      <c r="B908" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D908" s="1" t="s">
@@ -38499,7 +38467,7 @@
       <c r="A909" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B909" s="29" t="s">
+      <c r="B909" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D909" s="1" t="s">
@@ -38525,7 +38493,7 @@
       <c r="A910" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B910" s="29" t="s">
+      <c r="B910" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D910" s="1" t="s">
@@ -38551,7 +38519,7 @@
       <c r="A911" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B911" s="29" t="s">
+      <c r="B911" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D911" s="1" t="s">
@@ -38577,7 +38545,7 @@
       <c r="A912" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B912" s="29" t="s">
+      <c r="B912" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D912" s="1" t="s">
@@ -38603,7 +38571,7 @@
       <c r="A913" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B913" s="29" t="s">
+      <c r="B913" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D913" s="1" t="s">
@@ -38629,7 +38597,7 @@
       <c r="A914" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B914" s="29" t="s">
+      <c r="B914" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D914" s="1" t="s">
@@ -38655,7 +38623,7 @@
       <c r="A915" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B915" s="29" t="s">
+      <c r="B915" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D915" s="1" t="s">
@@ -38681,7 +38649,7 @@
       <c r="A916" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B916" s="29" t="s">
+      <c r="B916" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D916" s="1" t="s">
@@ -38707,7 +38675,7 @@
       <c r="A917" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B917" s="29" t="s">
+      <c r="B917" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D917" s="1" t="s">
@@ -38733,7 +38701,7 @@
       <c r="A918" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B918" s="29" t="s">
+      <c r="B918" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D918" s="1" t="s">
@@ -38759,7 +38727,7 @@
       <c r="A919" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B919" s="29" t="s">
+      <c r="B919" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D919" s="1" t="s">
@@ -38785,7 +38753,7 @@
       <c r="A920" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B920" s="29" t="s">
+      <c r="B920" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D920" s="1" t="s">
@@ -38811,7 +38779,7 @@
       <c r="A921" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B921" s="29" t="s">
+      <c r="B921" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D921" s="1" t="s">
@@ -38837,7 +38805,7 @@
       <c r="A922" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B922" s="29" t="s">
+      <c r="B922" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D922" s="1" t="s">
@@ -38863,7 +38831,7 @@
       <c r="A923" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B923" s="29" t="s">
+      <c r="B923" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D923" s="1" t="s">
@@ -38889,7 +38857,7 @@
       <c r="A924" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B924" s="29" t="s">
+      <c r="B924" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D924" s="1" t="s">
@@ -38915,7 +38883,7 @@
       <c r="A925" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B925" s="29" t="s">
+      <c r="B925" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D925" s="1" t="s">
@@ -38941,7 +38909,7 @@
       <c r="A926" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B926" s="29" t="s">
+      <c r="B926" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D926" s="1" t="s">
@@ -38967,7 +38935,7 @@
       <c r="A927" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B927" s="29" t="s">
+      <c r="B927" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D927" s="1" t="s">
@@ -38993,7 +38961,7 @@
       <c r="A928" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B928" s="29" t="s">
+      <c r="B928" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D928" s="1" t="s">
@@ -39019,7 +38987,7 @@
       <c r="A929" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B929" s="29" t="s">
+      <c r="B929" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D929" s="1" t="s">
@@ -39045,7 +39013,7 @@
       <c r="A930" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B930" s="29" t="s">
+      <c r="B930" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D930" s="1" t="s">
@@ -39071,7 +39039,7 @@
       <c r="A931" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B931" s="29" t="s">
+      <c r="B931" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D931" s="1" t="s">
@@ -39097,7 +39065,7 @@
       <c r="A932" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B932" s="29" t="s">
+      <c r="B932" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D932" s="1" t="s">
@@ -39123,7 +39091,7 @@
       <c r="A933" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B933" s="29" t="s">
+      <c r="B933" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D933" s="1" t="s">
@@ -39149,7 +39117,7 @@
       <c r="A934" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B934" s="29" t="s">
+      <c r="B934" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D934" s="1" t="s">
@@ -39175,7 +39143,7 @@
       <c r="A935" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B935" s="29" t="s">
+      <c r="B935" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D935" s="1" t="s">
@@ -39201,7 +39169,7 @@
       <c r="A936" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B936" s="29" t="s">
+      <c r="B936" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D936" s="1" t="s">
@@ -39227,7 +39195,7 @@
       <c r="A937" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B937" s="29" t="s">
+      <c r="B937" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D937" s="1" t="s">
@@ -39253,7 +39221,7 @@
       <c r="A938" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B938" s="29" t="s">
+      <c r="B938" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D938" s="1" t="s">
@@ -39279,7 +39247,7 @@
       <c r="A939" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B939" s="29" t="s">
+      <c r="B939" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D939" s="1" t="s">
@@ -39305,7 +39273,7 @@
       <c r="A940" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B940" s="29" t="s">
+      <c r="B940" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D940" s="1" t="s">
@@ -39331,7 +39299,7 @@
       <c r="A941" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B941" s="29" t="s">
+      <c r="B941" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D941" s="1" t="s">
@@ -39357,7 +39325,7 @@
       <c r="A942" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B942" s="29" t="s">
+      <c r="B942" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D942" s="1" t="s">
@@ -39383,7 +39351,7 @@
       <c r="A943" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B943" s="29" t="s">
+      <c r="B943" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D943" s="1" t="s">
@@ -39409,7 +39377,7 @@
       <c r="A944" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B944" s="29" t="s">
+      <c r="B944" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D944" s="1" t="s">
@@ -39435,7 +39403,7 @@
       <c r="A945" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B945" s="29" t="s">
+      <c r="B945" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D945" s="1" t="s">
@@ -39461,7 +39429,7 @@
       <c r="A946" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B946" s="29" t="s">
+      <c r="B946" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D946" s="1" t="s">
@@ -39487,7 +39455,7 @@
       <c r="A947" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B947" s="29" t="s">
+      <c r="B947" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D947" s="1" t="s">
@@ -39513,7 +39481,7 @@
       <c r="A948" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B948" s="29" t="s">
+      <c r="B948" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D948" s="1" t="s">
@@ -39539,7 +39507,7 @@
       <c r="A949" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B949" s="29" t="s">
+      <c r="B949" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D949" s="1" t="s">
@@ -39565,7 +39533,7 @@
       <c r="A950" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B950" s="29" t="s">
+      <c r="B950" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D950" s="1" t="s">
@@ -39591,7 +39559,7 @@
       <c r="A951" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B951" s="29" t="s">
+      <c r="B951" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D951" s="1" t="s">
@@ -39617,7 +39585,7 @@
       <c r="A952" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B952" s="29" t="s">
+      <c r="B952" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D952" s="1" t="s">
@@ -39643,7 +39611,7 @@
       <c r="A953" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B953" s="29" t="s">
+      <c r="B953" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D953" s="1" t="s">
@@ -39669,7 +39637,7 @@
       <c r="A954" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B954" s="29" t="s">
+      <c r="B954" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D954" s="1" t="s">
@@ -39695,7 +39663,7 @@
       <c r="A955" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B955" s="29" t="s">
+      <c r="B955" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D955" s="1" t="s">
@@ -39721,7 +39689,7 @@
       <c r="A956" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B956" s="29" t="s">
+      <c r="B956" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D956" s="1" t="s">
@@ -39747,7 +39715,7 @@
       <c r="A957" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B957" s="29" t="s">
+      <c r="B957" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D957" s="1" t="s">
@@ -39773,7 +39741,7 @@
       <c r="A958" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B958" s="29" t="s">
+      <c r="B958" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D958" s="1" t="s">
@@ -39799,7 +39767,7 @@
       <c r="A959" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B959" s="29" t="s">
+      <c r="B959" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D959" s="1" t="s">
@@ -39825,7 +39793,7 @@
       <c r="A960" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B960" s="29" t="s">
+      <c r="B960" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D960" s="1" t="s">
@@ -39851,7 +39819,7 @@
       <c r="A961" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B961" s="29" t="s">
+      <c r="B961" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D961" s="1" t="s">
@@ -39877,7 +39845,7 @@
       <c r="A962" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B962" s="29" t="s">
+      <c r="B962" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D962" s="1" t="s">
@@ -39903,7 +39871,7 @@
       <c r="A963" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B963" s="29" t="s">
+      <c r="B963" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D963" s="1" t="s">
@@ -39929,7 +39897,7 @@
       <c r="A964" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B964" s="29" t="s">
+      <c r="B964" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D964" s="1" t="s">
@@ -39955,7 +39923,7 @@
       <c r="A965" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B965" s="29" t="s">
+      <c r="B965" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D965" s="1" t="s">
@@ -39981,7 +39949,7 @@
       <c r="A966" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B966" s="29" t="s">
+      <c r="B966" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D966" s="1" t="s">
@@ -40007,7 +39975,7 @@
       <c r="A967" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B967" s="29" t="s">
+      <c r="B967" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D967" s="1" t="s">
@@ -40033,7 +40001,7 @@
       <c r="A968" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B968" s="29" t="s">
+      <c r="B968" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D968" s="1" t="s">
@@ -40059,7 +40027,7 @@
       <c r="A969" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B969" s="29" t="s">
+      <c r="B969" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D969" s="1" t="s">
@@ -40085,7 +40053,7 @@
       <c r="A970" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B970" s="29" t="s">
+      <c r="B970" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D970" s="1" t="s">
@@ -40111,7 +40079,7 @@
       <c r="A971" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B971" s="29" t="s">
+      <c r="B971" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D971" s="1" t="s">
@@ -40137,7 +40105,7 @@
       <c r="A972" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B972" s="29" t="s">
+      <c r="B972" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D972" s="1" t="s">
@@ -40163,7 +40131,7 @@
       <c r="A973" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B973" s="29" t="s">
+      <c r="B973" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D973" s="1" t="s">
@@ -40189,7 +40157,7 @@
       <c r="A974" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B974" s="29" t="s">
+      <c r="B974" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D974" s="1" t="s">
@@ -40215,7 +40183,7 @@
       <c r="A975" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B975" s="29" t="s">
+      <c r="B975" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D975" s="1" t="s">
@@ -40241,7 +40209,7 @@
       <c r="A976" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B976" s="29" t="s">
+      <c r="B976" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D976" s="1" t="s">
@@ -40267,7 +40235,7 @@
       <c r="A977" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B977" s="29" t="s">
+      <c r="B977" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D977" s="1" t="s">
@@ -40293,7 +40261,7 @@
       <c r="A978" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B978" s="29" t="s">
+      <c r="B978" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D978" s="1" t="s">
@@ -40319,7 +40287,7 @@
       <c r="A979" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B979" s="29" t="s">
+      <c r="B979" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D979" s="1" t="s">
@@ -40345,7 +40313,7 @@
       <c r="A980" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B980" s="29" t="s">
+      <c r="B980" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D980" s="1" t="s">
@@ -40371,7 +40339,7 @@
       <c r="A981" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B981" s="29" t="s">
+      <c r="B981" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D981" s="1" t="s">
@@ -40397,7 +40365,7 @@
       <c r="A982" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B982" s="29" t="s">
+      <c r="B982" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D982" s="1" t="s">
@@ -40423,7 +40391,7 @@
       <c r="A983" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B983" s="29" t="s">
+      <c r="B983" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D983" s="1" t="s">
@@ -40449,7 +40417,7 @@
       <c r="A984" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B984" s="29" t="s">
+      <c r="B984" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D984" s="1" t="s">
@@ -40475,7 +40443,7 @@
       <c r="A985" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B985" s="29" t="s">
+      <c r="B985" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D985" s="1" t="s">
@@ -40501,7 +40469,7 @@
       <c r="A986" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B986" s="29" t="s">
+      <c r="B986" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D986" s="1" t="s">
@@ -40527,7 +40495,7 @@
       <c r="A987" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B987" s="29" t="s">
+      <c r="B987" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D987" s="1" t="s">
@@ -40553,7 +40521,7 @@
       <c r="A988" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B988" s="29" t="s">
+      <c r="B988" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D988" s="1" t="s">
@@ -40579,7 +40547,7 @@
       <c r="A989" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B989" s="29" t="s">
+      <c r="B989" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D989" s="1" t="s">
@@ -40605,7 +40573,7 @@
       <c r="A990" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B990" s="29" t="s">
+      <c r="B990" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D990" s="1" t="s">
@@ -40631,7 +40599,7 @@
       <c r="A991" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B991" s="29" t="s">
+      <c r="B991" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D991" s="1" t="s">
@@ -40657,7 +40625,7 @@
       <c r="A992" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B992" s="29" t="s">
+      <c r="B992" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D992" s="1" t="s">
@@ -40683,7 +40651,7 @@
       <c r="A993" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B993" s="29" t="s">
+      <c r="B993" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D993" s="1" t="s">
@@ -40709,7 +40677,7 @@
       <c r="A994" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B994" s="29" t="s">
+      <c r="B994" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D994" s="1" t="s">
@@ -40735,7 +40703,7 @@
       <c r="A995" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B995" s="29" t="s">
+      <c r="B995" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D995" s="1" t="s">
@@ -40761,7 +40729,7 @@
       <c r="A996" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B996" s="29" t="s">
+      <c r="B996" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D996" s="1" t="s">
@@ -40787,7 +40755,7 @@
       <c r="A997" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B997" s="29" t="s">
+      <c r="B997" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D997" s="1" t="s">
@@ -40813,7 +40781,7 @@
       <c r="A998" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B998" s="29" t="s">
+      <c r="B998" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D998" s="1" t="s">
@@ -40839,7 +40807,7 @@
       <c r="A999" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B999" s="29" t="s">
+      <c r="B999" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D999" s="1" t="s">
@@ -40865,7 +40833,7 @@
       <c r="A1000" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B1000" s="29" t="s">
+      <c r="B1000" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D1000" s="1" t="s">
@@ -40891,7 +40859,7 @@
       <c r="A1001" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B1001" s="29" t="s">
+      <c r="B1001" s="32" t="s">
         <v>2992</v>
       </c>
       <c r="D1001" s="1" t="s">
@@ -40913,9 +40881,69 @@
         <v>1141</v>
       </c>
     </row>
+    <row r="1002" spans="1:19">
+      <c r="A1002" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B1002" s="32" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1002" s="3"/>
+      <c r="D1002" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J1002" s="3"/>
+      <c r="K1002" s="3"/>
+      <c r="L1002" s="3">
+        <v>83006678</v>
+      </c>
+      <c r="M1002" s="3"/>
+      <c r="P1002" s="1" t="s">
+        <v>2994</v>
+      </c>
+      <c r="Q1002" s="1" t="s">
+        <v>2996</v>
+      </c>
+      <c r="R1002" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="S1002" s="1" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:19">
+      <c r="A1003" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B1003" s="32" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1003" s="3"/>
+      <c r="D1003" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J1003" s="3"/>
+      <c r="K1003" s="3"/>
+      <c r="L1003" s="3">
+        <v>83006017</v>
+      </c>
+      <c r="M1003" s="3"/>
+      <c r="P1003" s="1" t="s">
+        <v>2995</v>
+      </c>
+      <c r="Q1003" s="1" t="s">
+        <v>2997</v>
+      </c>
+      <c r="R1003" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="S1003" s="1" t="s">
+        <v>1141</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D1002:D1048576">
+  <conditionalFormatting sqref="D1003:D1048576">
     <cfRule type="duplicateValues" dxfId="4" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 L1">
@@ -40956,8 +40984,8 @@
       <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>33</v>
+      <c r="C1" s="31" t="s">
+        <v>2993</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>1</v>
